--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_ADJR2.xlsx
@@ -211,7 +211,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +223,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,54 +248,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -605,9 +560,9 @@
   <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -665,49 +620,49 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>0.336542047211152</v>
+        <v>0.33752746789113541</v>
       </c>
       <c r="C2">
-        <v>0.50039699764965173</v>
+        <v>0.50127267550258181</v>
       </c>
       <c r="D2">
-        <v>0.5342093851056815</v>
+        <v>0.53689770103449874</v>
       </c>
       <c r="E2">
-        <v>0.57555010333045309</v>
+        <v>0.57902586480973928</v>
       </c>
       <c r="F2">
-        <v>0.5880937431836194</v>
+        <v>0.58824853999709781</v>
       </c>
       <c r="G2">
-        <v>0.61211873100187719</v>
+        <v>0.61311523553293712</v>
       </c>
       <c r="H2">
-        <v>0.6179141492280037</v>
+        <v>0.62055598102525922</v>
       </c>
       <c r="I2">
-        <v>0.6044931661267321</v>
+        <v>0.6090200881278659</v>
       </c>
       <c r="J2">
-        <v>0.58306941270395773</v>
+        <v>0.58339830542813975</v>
       </c>
       <c r="K2">
-        <v>0.55234635488322725</v>
+        <v>0.5543053785561084</v>
       </c>
       <c r="L2">
-        <v>0.56157188060072605</v>
+        <v>0.56313154247447406</v>
       </c>
       <c r="M2">
-        <v>0.5258601389126385</v>
+        <v>0.52297644828172607</v>
       </c>
       <c r="N2">
-        <v>0.49523106053146221</v>
+        <v>0.49609067029620663</v>
       </c>
       <c r="O2">
-        <v>0.49039077171233147</v>
+        <v>0.49582942369890759</v>
       </c>
       <c r="P2">
-        <v>0.51320459970049148</v>
+        <v>0.51401101628864809</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -715,49 +670,49 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>0.4175814138973471</v>
+        <v>0.41957734669781721</v>
       </c>
       <c r="C3">
-        <v>0.51703475833379386</v>
+        <v>0.51882981661691896</v>
       </c>
       <c r="D3">
-        <v>0.52185343761238334</v>
+        <v>0.52525713359456461</v>
       </c>
       <c r="E3">
-        <v>0.53082556313543217</v>
+        <v>0.52471288598069621</v>
       </c>
       <c r="F3">
-        <v>0.50519099971663761</v>
+        <v>0.50242334204022165</v>
       </c>
       <c r="G3">
-        <v>0.50240378706789468</v>
+        <v>0.49681484025899281</v>
       </c>
       <c r="H3">
-        <v>0.45061752576781772</v>
+        <v>0.44316694856344929</v>
       </c>
       <c r="I3">
-        <v>0.43613480537545313</v>
+        <v>0.42713803750678758</v>
       </c>
       <c r="J3">
-        <v>0.41771599328722547</v>
+        <v>0.40802394286690769</v>
       </c>
       <c r="K3">
-        <v>0.42552458135164478</v>
+        <v>0.41311154281148388</v>
       </c>
       <c r="L3">
-        <v>0.40508775264675662</v>
+        <v>0.39147809451842103</v>
       </c>
       <c r="M3">
-        <v>0.34356268608809809</v>
+        <v>0.32936347104689101</v>
       </c>
       <c r="N3">
-        <v>0.28118978663531652</v>
+        <v>0.26035581498960297</v>
       </c>
       <c r="O3">
-        <v>0.2265266890395326</v>
+        <v>0.20498379476734729</v>
       </c>
       <c r="P3">
-        <v>0.1731444118982727</v>
+        <v>0.14981843114882959</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -765,49 +720,49 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>0.35835112803278579</v>
+        <v>0.35914269094088958</v>
       </c>
       <c r="C4">
-        <v>0.48761849556341558</v>
+        <v>0.48696204257489162</v>
       </c>
       <c r="D4">
-        <v>0.50239109370192137</v>
+        <v>0.502426426342509</v>
       </c>
       <c r="E4">
-        <v>0.49954675782768171</v>
+        <v>0.49703148487053889</v>
       </c>
       <c r="F4">
-        <v>0.5135746897648561</v>
+        <v>0.51545882359221773</v>
       </c>
       <c r="G4">
-        <v>0.53640205845856803</v>
+        <v>0.53758854317164051</v>
       </c>
       <c r="H4">
-        <v>0.5612056845095994</v>
+        <v>0.56108385790689608</v>
       </c>
       <c r="I4">
-        <v>0.53991642236292237</v>
+        <v>0.54039283716011477</v>
       </c>
       <c r="J4">
-        <v>0.51714436848848522</v>
+        <v>0.51609148556110185</v>
       </c>
       <c r="K4">
-        <v>0.45320582557714029</v>
+        <v>0.44820647138381942</v>
       </c>
       <c r="L4">
-        <v>0.43406353340870002</v>
+        <v>0.43277455334644638</v>
       </c>
       <c r="M4">
-        <v>0.46693552812132211</v>
+        <v>0.46290229421563839</v>
       </c>
       <c r="N4">
-        <v>0.47335255305713142</v>
+        <v>0.46757651821857782</v>
       </c>
       <c r="O4">
-        <v>0.46132101631480382</v>
+        <v>0.45806175907763219</v>
       </c>
       <c r="P4">
-        <v>0.46480560920977437</v>
+        <v>0.46015117531830479</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -815,49 +770,49 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>0.50838833638851244</v>
+        <v>0.50957378081247262</v>
       </c>
       <c r="C5">
-        <v>0.51085619354449074</v>
+        <v>0.51315934291577314</v>
       </c>
       <c r="D5">
-        <v>0.51156564521004921</v>
+        <v>0.51071349060677496</v>
       </c>
       <c r="E5">
-        <v>0.5016705134880437</v>
+        <v>0.49953420265995091</v>
       </c>
       <c r="F5">
-        <v>0.49575635460150891</v>
+        <v>0.49196303339447661</v>
       </c>
       <c r="G5">
-        <v>0.49078120907983219</v>
+        <v>0.48794508736541731</v>
       </c>
       <c r="H5">
-        <v>0.48053778507483341</v>
+        <v>0.4740406172199958</v>
       </c>
       <c r="I5">
-        <v>0.4736132356322687</v>
+        <v>0.46444436302846931</v>
       </c>
       <c r="J5">
-        <v>0.4542570757477869</v>
+        <v>0.43900905760155862</v>
       </c>
       <c r="K5">
-        <v>0.44853836263270691</v>
+        <v>0.4293906815878325</v>
       </c>
       <c r="L5">
-        <v>0.43559412293978239</v>
+        <v>0.41283912220939301</v>
       </c>
       <c r="M5">
-        <v>0.42276549678751879</v>
+        <v>0.41164022939277822</v>
       </c>
       <c r="N5">
-        <v>0.41635020836635761</v>
+        <v>0.40434394069943341</v>
       </c>
       <c r="O5">
-        <v>0.39786547899581293</v>
+        <v>0.37891375765167712</v>
       </c>
       <c r="P5">
-        <v>0.41354057829161728</v>
+        <v>0.39605141387373849</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -865,49 +820,49 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.51012121367504781</v>
+        <v>0.51161756540262537</v>
       </c>
       <c r="C6">
-        <v>0.51652932019530307</v>
+        <v>0.51929472454801118</v>
       </c>
       <c r="D6">
-        <v>0.51922991958686282</v>
+        <v>0.52221614498941982</v>
       </c>
       <c r="E6">
-        <v>0.49691605050910459</v>
+        <v>0.50162755225359923</v>
       </c>
       <c r="F6">
-        <v>0.51494354520387287</v>
+        <v>0.51351350118965378</v>
       </c>
       <c r="G6">
-        <v>0.47909915007257758</v>
+        <v>0.47970396326487291</v>
       </c>
       <c r="H6">
-        <v>0.48291383977532643</v>
+        <v>0.48755045646446338</v>
       </c>
       <c r="I6">
-        <v>0.46120644235673319</v>
+        <v>0.46393805601232391</v>
       </c>
       <c r="J6">
-        <v>0.45543260692484838</v>
+        <v>0.46206382210455488</v>
       </c>
       <c r="K6">
-        <v>0.44457873578463358</v>
+        <v>0.450802608733609</v>
       </c>
       <c r="L6">
-        <v>0.40919165199892332</v>
+        <v>0.41524338283005258</v>
       </c>
       <c r="M6">
-        <v>0.36688589259011728</v>
+        <v>0.37984488654007448</v>
       </c>
       <c r="N6">
-        <v>0.34093526670714702</v>
+        <v>0.35064747062057061</v>
       </c>
       <c r="O6">
-        <v>0.33822022953187258</v>
+        <v>0.34600119735658191</v>
       </c>
       <c r="P6">
-        <v>0.37951477104932169</v>
+        <v>0.38366424298600899</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -915,49 +870,49 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>0.35564855715351928</v>
+        <v>0.35549196811818651</v>
       </c>
       <c r="C7">
-        <v>0.50039122687297122</v>
+        <v>0.50066486693535572</v>
       </c>
       <c r="D7">
-        <v>0.57323891842895691</v>
+        <v>0.5731317488647758</v>
       </c>
       <c r="E7">
-        <v>0.61696664193204842</v>
+        <v>0.61631159562716586</v>
       </c>
       <c r="F7">
-        <v>0.63686998478735424</v>
+        <v>0.63331021079577454</v>
       </c>
       <c r="G7">
-        <v>0.64672181776917559</v>
+        <v>0.64415500747855037</v>
       </c>
       <c r="H7">
-        <v>0.6307101088999264</v>
+        <v>0.62723397746655396</v>
       </c>
       <c r="I7">
-        <v>0.61247439998669229</v>
+        <v>0.6092394539952376</v>
       </c>
       <c r="J7">
-        <v>0.59516145115362873</v>
+        <v>0.59343257632877644</v>
       </c>
       <c r="K7">
-        <v>0.60383920401948499</v>
+        <v>0.5976480768881941</v>
       </c>
       <c r="L7">
-        <v>0.53973423420567934</v>
+        <v>0.53146892341862906</v>
       </c>
       <c r="M7">
-        <v>0.5491762797352463</v>
+        <v>0.54260230180341229</v>
       </c>
       <c r="N7">
-        <v>0.57307283392394326</v>
+        <v>0.5675090109304799</v>
       </c>
       <c r="O7">
-        <v>0.574475100044746</v>
+        <v>0.56737803528327013</v>
       </c>
       <c r="P7">
-        <v>0.57126272226084307</v>
+        <v>0.56349351364868416</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -965,49 +920,49 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>0.41239045253150969</v>
+        <v>0.41314942021117917</v>
       </c>
       <c r="C8">
-        <v>0.48052114144671743</v>
+        <v>0.48167730349479598</v>
       </c>
       <c r="D8">
-        <v>0.52443213913450581</v>
+        <v>0.52107869760133263</v>
       </c>
       <c r="E8">
-        <v>0.54239430241433606</v>
+        <v>0.53766725694537898</v>
       </c>
       <c r="F8">
-        <v>0.54724921024487594</v>
+        <v>0.54355415796655004</v>
       </c>
       <c r="G8">
-        <v>0.54217585767915033</v>
+        <v>0.53560551694420633</v>
       </c>
       <c r="H8">
-        <v>0.55083227025622639</v>
+        <v>0.54398449656462844</v>
       </c>
       <c r="I8">
-        <v>0.56426390223900502</v>
+        <v>0.55660815950998255</v>
       </c>
       <c r="J8">
-        <v>0.4992438765732054</v>
+        <v>0.49160259717392818</v>
       </c>
       <c r="K8">
-        <v>0.46471654984633798</v>
+        <v>0.44851607846767028</v>
       </c>
       <c r="L8">
-        <v>0.4692973057406028</v>
+        <v>0.45230676321580882</v>
       </c>
       <c r="M8">
-        <v>0.48199965986350451</v>
+        <v>0.4701911075680289</v>
       </c>
       <c r="N8">
-        <v>0.51039522666184511</v>
+        <v>0.49835785929857362</v>
       </c>
       <c r="O8">
-        <v>0.49360353892314901</v>
+        <v>0.47977541617484332</v>
       </c>
       <c r="P8">
-        <v>0.49656836500131812</v>
+        <v>0.48128587876427809</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1015,49 +970,49 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>0.41370913850539648</v>
+        <v>0.41260322920368148</v>
       </c>
       <c r="C9">
-        <v>0.48142731596941729</v>
+        <v>0.47900703448338727</v>
       </c>
       <c r="D9">
-        <v>0.51967981567643362</v>
+        <v>0.51868483101699792</v>
       </c>
       <c r="E9">
-        <v>0.53452841215237989</v>
+        <v>0.53312019719389137</v>
       </c>
       <c r="F9">
-        <v>0.5433440519882774</v>
+        <v>0.54015477130058231</v>
       </c>
       <c r="G9">
-        <v>0.53778689428770721</v>
+        <v>0.53518913907105159</v>
       </c>
       <c r="H9">
-        <v>0.54333544700055392</v>
+        <v>0.54303921467699567</v>
       </c>
       <c r="I9">
-        <v>0.55800134282810709</v>
+        <v>0.55472267139643772</v>
       </c>
       <c r="J9">
-        <v>0.51397597242030735</v>
+        <v>0.51092278500258781</v>
       </c>
       <c r="K9">
-        <v>0.47148651359290877</v>
+        <v>0.47485782141792993</v>
       </c>
       <c r="L9">
-        <v>0.45216138479075191</v>
+        <v>0.45428305356241527</v>
       </c>
       <c r="M9">
-        <v>0.47052398002248158</v>
+        <v>0.47228365591781968</v>
       </c>
       <c r="N9">
-        <v>0.50777804483182742</v>
+        <v>0.50940359575355276</v>
       </c>
       <c r="O9">
-        <v>0.49419948346884779</v>
+        <v>0.49742193145004288</v>
       </c>
       <c r="P9">
-        <v>0.48641889629055562</v>
+        <v>0.48710703750556011</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1065,49 +1020,49 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>0.41259550942915613</v>
+        <v>0.41325271244798401</v>
       </c>
       <c r="C10">
-        <v>0.48177460121260302</v>
+        <v>0.48182750537734548</v>
       </c>
       <c r="D10">
-        <v>0.5200586798857133</v>
+        <v>0.52620804420945311</v>
       </c>
       <c r="E10">
-        <v>0.53685759801228639</v>
+        <v>0.54231374484813311</v>
       </c>
       <c r="F10">
-        <v>0.53991973064844934</v>
+        <v>0.54677965501214709</v>
       </c>
       <c r="G10">
-        <v>0.53465578177385975</v>
+        <v>0.54108265591882265</v>
       </c>
       <c r="H10">
-        <v>0.54266325061011822</v>
+        <v>0.54875810744190301</v>
       </c>
       <c r="I10">
-        <v>0.55779402292691049</v>
+        <v>0.56439235864259885</v>
       </c>
       <c r="J10">
-        <v>0.51356661671858317</v>
+        <v>0.52305209103462924</v>
       </c>
       <c r="K10">
-        <v>0.47549740263594181</v>
+        <v>0.48935352180793812</v>
       </c>
       <c r="L10">
-        <v>0.45633754307127461</v>
+        <v>0.46433171367733572</v>
       </c>
       <c r="M10">
-        <v>0.47376960996173062</v>
+        <v>0.48166029474883931</v>
       </c>
       <c r="N10">
-        <v>0.51318277884698937</v>
+        <v>0.51736986667350338</v>
       </c>
       <c r="O10">
-        <v>0.50776774726857965</v>
+        <v>0.51165387665234319</v>
       </c>
       <c r="P10">
-        <v>0.49731344830025792</v>
+        <v>0.49673903778937101</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1115,49 +1070,49 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>0.41312584283080928</v>
+        <v>0.41208113491732379</v>
       </c>
       <c r="C11">
-        <v>0.48006522854331712</v>
+        <v>0.48063038175118239</v>
       </c>
       <c r="D11">
-        <v>0.52140877113152473</v>
+        <v>0.521870539692322</v>
       </c>
       <c r="E11">
-        <v>0.53654337317782219</v>
+        <v>0.53648880274073019</v>
       </c>
       <c r="F11">
-        <v>0.54286939318602567</v>
+        <v>0.53923704882810874</v>
       </c>
       <c r="G11">
-        <v>0.5350157892008307</v>
+        <v>0.53139569240491669</v>
       </c>
       <c r="H11">
-        <v>0.54077218113812719</v>
+        <v>0.53771585502094199</v>
       </c>
       <c r="I11">
-        <v>0.55938018041020399</v>
+        <v>0.55546076781556541</v>
       </c>
       <c r="J11">
-        <v>0.51375020052486109</v>
+        <v>0.51338913796927754</v>
       </c>
       <c r="K11">
-        <v>0.48129822952318629</v>
+        <v>0.47605769413716359</v>
       </c>
       <c r="L11">
-        <v>0.46829438487583808</v>
+        <v>0.46207654210884558</v>
       </c>
       <c r="M11">
-        <v>0.48683342025611209</v>
+        <v>0.47917871576351623</v>
       </c>
       <c r="N11">
-        <v>0.51080635298763688</v>
+        <v>0.50663338260690705</v>
       </c>
       <c r="O11">
-        <v>0.49437976254956562</v>
+        <v>0.486323826882052</v>
       </c>
       <c r="P11">
-        <v>0.51355132291665051</v>
+        <v>0.5065498521042523</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1165,49 +1120,49 @@
         <v>26</v>
       </c>
       <c r="B12">
-        <v>0.5194368037192677</v>
+        <v>0.51729910153209291</v>
       </c>
       <c r="C12">
-        <v>0.52669693585558053</v>
+        <v>0.52415700877901705</v>
       </c>
       <c r="D12">
-        <v>0.5293189712441182</v>
+        <v>0.52727268412032269</v>
       </c>
       <c r="E12">
-        <v>0.52982349275219398</v>
+        <v>0.52566381738400114</v>
       </c>
       <c r="F12">
-        <v>0.53743582516132216</v>
+        <v>0.53469652574865156</v>
       </c>
       <c r="G12">
-        <v>0.53793900659278415</v>
+        <v>0.53703418410459869</v>
       </c>
       <c r="H12">
-        <v>0.53440312357222008</v>
+        <v>0.53618296209151306</v>
       </c>
       <c r="I12">
-        <v>0.52332150749985928</v>
+        <v>0.52820572321641257</v>
       </c>
       <c r="J12">
-        <v>0.51370739794889875</v>
+        <v>0.51565486110253755</v>
       </c>
       <c r="K12">
-        <v>0.49715905706489649</v>
+        <v>0.49880627971811659</v>
       </c>
       <c r="L12">
-        <v>0.46411928046382073</v>
+        <v>0.4736869045173514</v>
       </c>
       <c r="M12">
-        <v>0.44184070209036092</v>
+        <v>0.44640444270746188</v>
       </c>
       <c r="N12">
-        <v>0.43157769562077358</v>
+        <v>0.44268746067956771</v>
       </c>
       <c r="O12">
-        <v>0.41342684896086213</v>
+        <v>0.4194996516991682</v>
       </c>
       <c r="P12">
-        <v>0.41085219757932973</v>
+        <v>0.42226825103177568</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1215,49 +1170,49 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>0.51771900165430873</v>
+        <v>0.51680489875330338</v>
       </c>
       <c r="C13">
-        <v>0.53925951873555589</v>
+        <v>0.53669345174357608</v>
       </c>
       <c r="D13">
-        <v>0.55010873654193371</v>
+        <v>0.54532994312533301</v>
       </c>
       <c r="E13">
-        <v>0.55320033285145831</v>
+        <v>0.5486934942337518</v>
       </c>
       <c r="F13">
-        <v>0.54114987294063632</v>
+        <v>0.53918742424388466</v>
       </c>
       <c r="G13">
-        <v>0.53172303849612912</v>
+        <v>0.52773801694017741</v>
       </c>
       <c r="H13">
-        <v>0.52624039826489555</v>
+        <v>0.52307779528447473</v>
       </c>
       <c r="I13">
-        <v>0.50642285233416873</v>
+        <v>0.50283217350517651</v>
       </c>
       <c r="J13">
-        <v>0.49509586493004831</v>
+        <v>0.48955872549932788</v>
       </c>
       <c r="K13">
-        <v>0.46829429697775937</v>
+        <v>0.46357385235304788</v>
       </c>
       <c r="L13">
-        <v>0.45854815787616232</v>
+        <v>0.45293689265855658</v>
       </c>
       <c r="M13">
-        <v>0.45196313100988628</v>
+        <v>0.44520695838845392</v>
       </c>
       <c r="N13">
-        <v>0.44101930985904458</v>
+        <v>0.43184619855842071</v>
       </c>
       <c r="O13">
-        <v>0.42227659237733461</v>
+        <v>0.4155873245464845</v>
       </c>
       <c r="P13">
-        <v>0.39212015506829978</v>
+        <v>0.37907779107356632</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1265,49 +1220,49 @@
         <v>28</v>
       </c>
       <c r="B14">
-        <v>0.35776900977035009</v>
+        <v>0.35869959951119917</v>
       </c>
       <c r="C14">
-        <v>0.50268265906174436</v>
+        <v>0.50314235936684371</v>
       </c>
       <c r="D14">
-        <v>0.57312721724704729</v>
+        <v>0.57618662798384113</v>
       </c>
       <c r="E14">
-        <v>0.61695906978318005</v>
+        <v>0.62004074434758627</v>
       </c>
       <c r="F14">
-        <v>0.63444020965619197</v>
+        <v>0.63827515769940513</v>
       </c>
       <c r="G14">
-        <v>0.64317883235309803</v>
+        <v>0.64390748862054004</v>
       </c>
       <c r="H14">
-        <v>0.62770908619545784</v>
+        <v>0.63327654576991865</v>
       </c>
       <c r="I14">
-        <v>0.61463238507247919</v>
+        <v>0.61547241078221504</v>
       </c>
       <c r="J14">
-        <v>0.59718672887216107</v>
+        <v>0.59752913917954176</v>
       </c>
       <c r="K14">
-        <v>0.59460078062350608</v>
+        <v>0.59193551640593556</v>
       </c>
       <c r="L14">
-        <v>0.51954570419136625</v>
+        <v>0.51891153207600149</v>
       </c>
       <c r="M14">
-        <v>0.51220011171669322</v>
+        <v>0.51417326933619378</v>
       </c>
       <c r="N14">
-        <v>0.54035507309057762</v>
+        <v>0.53902994027421725</v>
       </c>
       <c r="O14">
-        <v>0.54894862686504797</v>
+        <v>0.55182435903316507</v>
       </c>
       <c r="P14">
-        <v>0.56417347460227318</v>
+        <v>0.56720079470902462</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1315,49 +1270,49 @@
         <v>29</v>
       </c>
       <c r="B15">
-        <v>0.35613338625695018</v>
+        <v>0.35442647896270141</v>
       </c>
       <c r="C15">
-        <v>0.50054877455216984</v>
+        <v>0.49889225550075372</v>
       </c>
       <c r="D15">
-        <v>0.5729092961734642</v>
+        <v>0.57328960482521552</v>
       </c>
       <c r="E15">
-        <v>0.61797649495333484</v>
+        <v>0.6161644892993795</v>
       </c>
       <c r="F15">
-        <v>0.63470912432031223</v>
+        <v>0.63396181713156852</v>
       </c>
       <c r="G15">
-        <v>0.64265113835366916</v>
+        <v>0.64149892936945685</v>
       </c>
       <c r="H15">
-        <v>0.62793525289609597</v>
+        <v>0.62616790667252498</v>
       </c>
       <c r="I15">
-        <v>0.61440821007005042</v>
+        <v>0.61069865037460835</v>
       </c>
       <c r="J15">
-        <v>0.59742749029251052</v>
+        <v>0.59736349329601779</v>
       </c>
       <c r="K15">
-        <v>0.59120955821287902</v>
+        <v>0.59229621778649932</v>
       </c>
       <c r="L15">
-        <v>0.52259590918506926</v>
+        <v>0.52462942729449291</v>
       </c>
       <c r="M15">
-        <v>0.50681442447043024</v>
+        <v>0.51105960129114125</v>
       </c>
       <c r="N15">
-        <v>0.52915532836948875</v>
+        <v>0.53367287297373833</v>
       </c>
       <c r="O15">
-        <v>0.5400824663638597</v>
+        <v>0.54370123970766682</v>
       </c>
       <c r="P15">
-        <v>0.55879828282467547</v>
+        <v>0.56088212026636586</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1365,49 +1320,49 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>0.35825736951648618</v>
+        <v>0.36017689441097372</v>
       </c>
       <c r="C16">
-        <v>0.50411165745950037</v>
+        <v>0.50481121432938336</v>
       </c>
       <c r="D16">
-        <v>0.57964590909479519</v>
+        <v>0.57660016052233454</v>
       </c>
       <c r="E16">
-        <v>0.61992227256468602</v>
+        <v>0.61787842464422249</v>
       </c>
       <c r="F16">
-        <v>0.63813743559947644</v>
+        <v>0.63672143237439371</v>
       </c>
       <c r="G16">
-        <v>0.64487142538954989</v>
+        <v>0.64588986526667591</v>
       </c>
       <c r="H16">
-        <v>0.63146889425357444</v>
+        <v>0.6310117050660583</v>
       </c>
       <c r="I16">
-        <v>0.6158459679413455</v>
+        <v>0.6182443481816301</v>
       </c>
       <c r="J16">
-        <v>0.59937079225209056</v>
+        <v>0.60382098669524675</v>
       </c>
       <c r="K16">
-        <v>0.59186309943659465</v>
+        <v>0.60015344607679955</v>
       </c>
       <c r="L16">
-        <v>0.52467700796491634</v>
+        <v>0.53424687594308595</v>
       </c>
       <c r="M16">
-        <v>0.51449513049101614</v>
+        <v>0.52442770762340052</v>
       </c>
       <c r="N16">
-        <v>0.53449563704644187</v>
+        <v>0.54731509186102012</v>
       </c>
       <c r="O16">
-        <v>0.54173010919306586</v>
+        <v>0.55457395604829696</v>
       </c>
       <c r="P16">
-        <v>0.55660954455197786</v>
+        <v>0.5698701170992817</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1415,49 +1370,49 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>0.35941648369516399</v>
+        <v>0.3571896038377142</v>
       </c>
       <c r="C17">
-        <v>0.50382784076086862</v>
+        <v>0.50171261455023908</v>
       </c>
       <c r="D17">
-        <v>0.57497500426987991</v>
+        <v>0.57667027717426156</v>
       </c>
       <c r="E17">
-        <v>0.61624315387709994</v>
+        <v>0.61894593821427801</v>
       </c>
       <c r="F17">
-        <v>0.6327685662796636</v>
+        <v>0.63649525970291432</v>
       </c>
       <c r="G17">
-        <v>0.6427840668428475</v>
+        <v>0.64524631837489432</v>
       </c>
       <c r="H17">
-        <v>0.6279602297088055</v>
+        <v>0.63260501262731283</v>
       </c>
       <c r="I17">
-        <v>0.6145967435081543</v>
+        <v>0.62014516098486927</v>
       </c>
       <c r="J17">
-        <v>0.59743952615374596</v>
+        <v>0.60464731803167693</v>
       </c>
       <c r="K17">
-        <v>0.59320938652130262</v>
+        <v>0.60268752776100831</v>
       </c>
       <c r="L17">
-        <v>0.52248120324993108</v>
+        <v>0.53991933753520405</v>
       </c>
       <c r="M17">
-        <v>0.51188806626211369</v>
+        <v>0.52983388569782364</v>
       </c>
       <c r="N17">
-        <v>0.53855007233236585</v>
+        <v>0.55553053606916614</v>
       </c>
       <c r="O17">
-        <v>0.5478123922565723</v>
+        <v>0.56467676088886565</v>
       </c>
       <c r="P17">
-        <v>0.56636478729039308</v>
+        <v>0.57965464274420764</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1465,49 +1420,49 @@
         <v>32</v>
       </c>
       <c r="B18">
-        <v>0.52076462385531874</v>
+        <v>0.51797864607635247</v>
       </c>
       <c r="C18">
-        <v>0.52721116360203046</v>
+        <v>0.52386311910304018</v>
       </c>
       <c r="D18">
-        <v>0.53026245232681657</v>
+        <v>0.52123277150530156</v>
       </c>
       <c r="E18">
-        <v>0.53132808419548805</v>
+        <v>0.5209988266489799</v>
       </c>
       <c r="F18">
-        <v>0.55115925727835258</v>
+        <v>0.54233280752728052</v>
       </c>
       <c r="G18">
-        <v>0.53519631837403714</v>
+        <v>0.52747156769285641</v>
       </c>
       <c r="H18">
-        <v>0.54625270989954655</v>
+        <v>0.53574013434755863</v>
       </c>
       <c r="I18">
-        <v>0.54215162247212212</v>
+        <v>0.53706263232190377</v>
       </c>
       <c r="J18">
-        <v>0.54320703790314528</v>
+        <v>0.53780906218453894</v>
       </c>
       <c r="K18">
-        <v>0.54471143584922366</v>
+        <v>0.53879414671012771</v>
       </c>
       <c r="L18">
-        <v>0.54160494738325393</v>
+        <v>0.54034079305098948</v>
       </c>
       <c r="M18">
-        <v>0.53225207955389253</v>
+        <v>0.52831381882334616</v>
       </c>
       <c r="N18">
-        <v>0.52970934844375384</v>
+        <v>0.52532290999306563</v>
       </c>
       <c r="O18">
-        <v>0.50647002517093154</v>
+        <v>0.5050732876023164</v>
       </c>
       <c r="P18">
-        <v>0.51096248340530626</v>
+        <v>0.51510697498485503</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1515,49 +1470,49 @@
         <v>33</v>
       </c>
       <c r="B19">
-        <v>0.5218828313171332</v>
+        <v>0.52203899715557101</v>
       </c>
       <c r="C19">
-        <v>0.53212662213059914</v>
+        <v>0.53259622556518105</v>
       </c>
       <c r="D19">
-        <v>0.53655021922332458</v>
+        <v>0.53859304909455052</v>
       </c>
       <c r="E19">
-        <v>0.52093857710259517</v>
+        <v>0.52443502891551241</v>
       </c>
       <c r="F19">
-        <v>0.54239759558427003</v>
+        <v>0.54130634918875364</v>
       </c>
       <c r="G19">
-        <v>0.5343871874731343</v>
+        <v>0.53497720455812348</v>
       </c>
       <c r="H19">
-        <v>0.54534534762077902</v>
+        <v>0.54513031898998598</v>
       </c>
       <c r="I19">
-        <v>0.54422437009251723</v>
+        <v>0.53902049172659428</v>
       </c>
       <c r="J19">
-        <v>0.54329531342882131</v>
+        <v>0.53987984630845054</v>
       </c>
       <c r="K19">
-        <v>0.55807364369131496</v>
+        <v>0.55371879348298003</v>
       </c>
       <c r="L19">
-        <v>0.53177912889817258</v>
+        <v>0.52803323903077437</v>
       </c>
       <c r="M19">
-        <v>0.5154042024903569</v>
+        <v>0.51381054771521961</v>
       </c>
       <c r="N19">
-        <v>0.5128599648402784</v>
+        <v>0.5107716838981432</v>
       </c>
       <c r="O19">
-        <v>0.50500578589315437</v>
+        <v>0.50393672550320956</v>
       </c>
       <c r="P19">
-        <v>0.51484696531464547</v>
+        <v>0.51513828881996937</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -1565,49 +1520,49 @@
         <v>34</v>
       </c>
       <c r="B20">
-        <v>0.52338954805468041</v>
+        <v>0.5225277358788446</v>
       </c>
       <c r="C20">
-        <v>0.53477191270982072</v>
+        <v>0.53493320106181108</v>
       </c>
       <c r="D20">
-        <v>0.54676383741550572</v>
+        <v>0.55016631578332342</v>
       </c>
       <c r="E20">
-        <v>0.52657826829778387</v>
+        <v>0.52605565946482247</v>
       </c>
       <c r="F20">
-        <v>0.52849068876410832</v>
+        <v>0.52621475676318796</v>
       </c>
       <c r="G20">
-        <v>0.5487337994727286</v>
+        <v>0.54353396930093412</v>
       </c>
       <c r="H20">
-        <v>0.56907196780259539</v>
+        <v>0.56896812314820444</v>
       </c>
       <c r="I20">
-        <v>0.55113136261426843</v>
+        <v>0.54909775222047674</v>
       </c>
       <c r="J20">
-        <v>0.55735960185834399</v>
+        <v>0.55658150736013512</v>
       </c>
       <c r="K20">
-        <v>0.55573123794763712</v>
+        <v>0.55522931297586853</v>
       </c>
       <c r="L20">
-        <v>0.53956095453874131</v>
+        <v>0.54069917936182754</v>
       </c>
       <c r="M20">
-        <v>0.51506612925174722</v>
+        <v>0.51699753845212704</v>
       </c>
       <c r="N20">
-        <v>0.5066431648392431</v>
+        <v>0.51417587883998361</v>
       </c>
       <c r="O20">
-        <v>0.53107585649745559</v>
+        <v>0.54261083014400546</v>
       </c>
       <c r="P20">
-        <v>0.53360471001171828</v>
+        <v>0.54256126142993943</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -1615,49 +1570,49 @@
         <v>35</v>
       </c>
       <c r="B21">
-        <v>0.419000767693118</v>
+        <v>0.42057709490614797</v>
       </c>
       <c r="C21">
-        <v>0.51603996515066308</v>
+        <v>0.51670098699458011</v>
       </c>
       <c r="D21">
-        <v>0.52397425680955345</v>
+        <v>0.52670537964542485</v>
       </c>
       <c r="E21">
-        <v>0.53810987526806964</v>
+        <v>0.54020088382550813</v>
       </c>
       <c r="F21">
-        <v>0.5252030676746241</v>
+        <v>0.53193775329528903</v>
       </c>
       <c r="G21">
-        <v>0.51157291187178777</v>
+        <v>0.52260856909014364</v>
       </c>
       <c r="H21">
-        <v>0.44571692157210069</v>
+        <v>0.46099523724767749</v>
       </c>
       <c r="I21">
-        <v>0.42727718353389138</v>
+        <v>0.44425323456914811</v>
       </c>
       <c r="J21">
-        <v>0.42514802313504563</v>
+        <v>0.4376444977574877</v>
       </c>
       <c r="K21">
-        <v>0.40154664593483508</v>
+        <v>0.415752173742516</v>
       </c>
       <c r="L21">
-        <v>0.36781608831317031</v>
+        <v>0.3808380262744897</v>
       </c>
       <c r="M21">
-        <v>0.33091278735480117</v>
+        <v>0.3452501080304623</v>
       </c>
       <c r="N21">
-        <v>0.28615081414855842</v>
+        <v>0.29736638558231149</v>
       </c>
       <c r="O21">
-        <v>0.2249657677192628</v>
+        <v>0.2317809479946496</v>
       </c>
       <c r="P21">
-        <v>0.1544592110285104</v>
+        <v>0.16228976580741161</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -1665,49 +1620,49 @@
         <v>36</v>
       </c>
       <c r="B22">
-        <v>0.41753576788333302</v>
+        <v>0.41875423864881539</v>
       </c>
       <c r="C22">
-        <v>0.51485874364646378</v>
+        <v>0.5162608916060436</v>
       </c>
       <c r="D22">
-        <v>0.52464955660918966</v>
+        <v>0.5249619196751677</v>
       </c>
       <c r="E22">
-        <v>0.53864230268307134</v>
+        <v>0.53471061786487173</v>
       </c>
       <c r="F22">
-        <v>0.5318423257240088</v>
+        <v>0.52637198764000293</v>
       </c>
       <c r="G22">
-        <v>0.53442583716979175</v>
+        <v>0.52901684892551459</v>
       </c>
       <c r="H22">
-        <v>0.46767387660852849</v>
+        <v>0.46101959360772438</v>
       </c>
       <c r="I22">
-        <v>0.43687643365302109</v>
+        <v>0.43184112283558052</v>
       </c>
       <c r="J22">
-        <v>0.43950815008285748</v>
+        <v>0.42911575555027082</v>
       </c>
       <c r="K22">
-        <v>0.42151108709307128</v>
+        <v>0.41292871838913758</v>
       </c>
       <c r="L22">
-        <v>0.38416002209217892</v>
+        <v>0.37506981531875327</v>
       </c>
       <c r="M22">
-        <v>0.34672801929433378</v>
+        <v>0.33921220800694352</v>
       </c>
       <c r="N22">
-        <v>0.30839620650062433</v>
+        <v>0.29492150341147799</v>
       </c>
       <c r="O22">
-        <v>0.24532209163533411</v>
+        <v>0.2274300287745189</v>
       </c>
       <c r="P22">
-        <v>0.19357966820673719</v>
+        <v>0.17045172081754331</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -1715,49 +1670,49 @@
         <v>37</v>
       </c>
       <c r="B23">
-        <v>0.51797778004400463</v>
+        <v>0.51505765195566022</v>
       </c>
       <c r="C23">
-        <v>0.48633204679796432</v>
+        <v>0.47886634144836487</v>
       </c>
       <c r="D23">
-        <v>0.51473046207046302</v>
+        <v>0.51019179835413897</v>
       </c>
       <c r="E23">
-        <v>0.52764044766300922</v>
+        <v>0.52683194232927899</v>
       </c>
       <c r="F23">
-        <v>0.48793283047920988</v>
+        <v>0.48409841153792771</v>
       </c>
       <c r="G23">
-        <v>0.43317904382169192</v>
+        <v>0.43448589533513238</v>
       </c>
       <c r="H23">
-        <v>0.36611540091438971</v>
+        <v>0.36267851399087231</v>
       </c>
       <c r="I23">
-        <v>0.34931662380896739</v>
+        <v>0.35102325823823077</v>
       </c>
       <c r="J23">
-        <v>0.29946952953178407</v>
+        <v>0.30166349291404149</v>
       </c>
       <c r="K23">
-        <v>0.26858026253556389</v>
+        <v>0.26669643373730889</v>
       </c>
       <c r="L23">
-        <v>0.2288568713970017</v>
+        <v>0.22328236370976309</v>
       </c>
       <c r="M23">
-        <v>0.21010078211868119</v>
+        <v>0.20519943985969299</v>
       </c>
       <c r="N23">
-        <v>0.16512477805178341</v>
+        <v>0.15566501895974319</v>
       </c>
       <c r="O23">
-        <v>0.1139843168897878</v>
+        <v>0.10713528250855441</v>
       </c>
       <c r="P23">
-        <v>5.5330668225047279E-2</v>
+        <v>4.7219323811258179E-2</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -1765,49 +1720,49 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>8.0624288383575632E-2</v>
+        <v>7.9644270843617831E-2</v>
       </c>
       <c r="C24">
-        <v>5.2963866666081386E-3</v>
+        <v>1.0457558088178239E-2</v>
       </c>
       <c r="D24">
-        <v>3.0578594429165201E-2</v>
+        <v>2.983693508975541E-2</v>
       </c>
       <c r="E24">
-        <v>-7.4020830896416506E-2</v>
+        <v>-8.402635933129092E-2</v>
       </c>
       <c r="F24">
-        <v>-0.36956677810289768</v>
+        <v>-0.36944332593524548</v>
       </c>
       <c r="G24">
-        <v>-0.25930679438282489</v>
+        <v>-0.25591932650439952</v>
       </c>
       <c r="H24">
-        <v>-0.32779576041875741</v>
+        <v>-0.32304446917578711</v>
       </c>
       <c r="I24">
-        <v>-0.38925080376058813</v>
+        <v>-0.37949463010762691</v>
       </c>
       <c r="J24">
-        <v>-0.4540289626180174</v>
+        <v>-0.42402360897274638</v>
       </c>
       <c r="K24">
-        <v>-0.50869857638311466</v>
+        <v>-0.48780252787470751</v>
       </c>
       <c r="L24">
-        <v>-0.5698399756995155</v>
+        <v>-0.54808675460587764</v>
       </c>
       <c r="M24">
-        <v>-0.56841957402407373</v>
+        <v>-0.55072484803656596</v>
       </c>
       <c r="N24">
-        <v>-0.5628800768400406</v>
+        <v>-0.53904803974386428</v>
       </c>
       <c r="O24">
-        <v>-0.58833608721535935</v>
+        <v>-0.57144008787599532</v>
       </c>
       <c r="P24">
-        <v>-0.61288586642147613</v>
+        <v>-0.59059135381604821</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -1815,49 +1770,49 @@
         <v>39</v>
       </c>
       <c r="B25">
-        <v>5.8059178361178139E-2</v>
+        <v>5.8540258842796518E-2</v>
       </c>
       <c r="C25">
-        <v>8.9470281882851577E-4</v>
+        <v>8.6863039193726208E-3</v>
       </c>
       <c r="D25">
-        <v>-4.4491523712725869E-2</v>
+        <v>-3.573713536710358E-2</v>
       </c>
       <c r="E25">
-        <v>-0.14831462548964441</v>
+        <v>-0.13505477135410671</v>
       </c>
       <c r="F25">
-        <v>-0.22177984922957689</v>
+        <v>-0.2165552082413672</v>
       </c>
       <c r="G25">
-        <v>-0.37270763205100998</v>
+        <v>-0.36716566553368091</v>
       </c>
       <c r="H25">
-        <v>-0.4976677266756549</v>
+        <v>-0.48150694953216688</v>
       </c>
       <c r="I25">
-        <v>-0.58611238722286441</v>
+        <v>-0.5654212439002545</v>
       </c>
       <c r="J25">
-        <v>-0.60405430437917951</v>
+        <v>-0.57714772591060237</v>
       </c>
       <c r="K25">
-        <v>-0.60035814417130018</v>
+        <v>-0.57067366728546787</v>
       </c>
       <c r="L25">
-        <v>-0.6835327724651532</v>
+        <v>-0.66586555932537128</v>
       </c>
       <c r="M25">
-        <v>-0.7693219241007011</v>
+        <v>-0.76437479493410587</v>
       </c>
       <c r="N25">
-        <v>-0.84807252851492498</v>
+        <v>-0.84996996481406828</v>
       </c>
       <c r="O25">
-        <v>-0.86739389392849586</v>
+        <v>-0.86416685212238076</v>
       </c>
       <c r="P25">
-        <v>-0.88728826897063817</v>
+        <v>-0.88009174105524068</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -1865,49 +1820,49 @@
         <v>40</v>
       </c>
       <c r="B26">
-        <v>6.5400659920807569E-2</v>
+        <v>7.108703845491024E-2</v>
       </c>
       <c r="C26">
-        <v>2.5969707636913371E-2</v>
+        <v>3.8460448793727148E-2</v>
       </c>
       <c r="D26">
-        <v>2.2979533505303219E-2</v>
+        <v>2.9359571346470919E-2</v>
       </c>
       <c r="E26">
-        <v>-7.7666319388756636E-2</v>
+        <v>-6.529398830007685E-2</v>
       </c>
       <c r="F26">
-        <v>-0.15173611164005249</v>
+        <v>-0.15351093809088179</v>
       </c>
       <c r="G26">
-        <v>-0.1720661848565132</v>
+        <v>-0.17683522653200789</v>
       </c>
       <c r="H26">
-        <v>-0.24190329900647201</v>
+        <v>-0.23923241628540889</v>
       </c>
       <c r="I26">
-        <v>-0.21774594531649319</v>
+        <v>-0.20442471186157379</v>
       </c>
       <c r="J26">
-        <v>-0.1657577265303348</v>
+        <v>-0.1508328446926665</v>
       </c>
       <c r="K26">
-        <v>-0.10855073071028989</v>
+        <v>-0.1001837964242487</v>
       </c>
       <c r="L26">
-        <v>-0.2773617471432569</v>
+        <v>-0.25983736372444011</v>
       </c>
       <c r="M26">
-        <v>-0.43379613160015268</v>
+        <v>-0.42946163823866651</v>
       </c>
       <c r="N26">
-        <v>-0.38442161775515388</v>
+        <v>-0.37654590076280642</v>
       </c>
       <c r="O26">
-        <v>-0.40530256546956722</v>
+        <v>-0.41109419022900501</v>
       </c>
       <c r="P26">
-        <v>-0.42134049253555361</v>
+        <v>-0.43094556808729451</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -1915,49 +1870,49 @@
         <v>41</v>
       </c>
       <c r="B27">
-        <v>5.3249996044979438E-2</v>
+        <v>5.2031678223643733E-2</v>
       </c>
       <c r="C27">
-        <v>2.5559477351838229E-2</v>
+        <v>2.682422418858911E-2</v>
       </c>
       <c r="D27">
-        <v>-9.9595939772773534E-2</v>
+        <v>-9.2785178565100879E-2</v>
       </c>
       <c r="E27">
-        <v>-4.8252959595725571E-2</v>
+        <v>-4.9464444755769353E-2</v>
       </c>
       <c r="F27">
-        <v>-0.1626203464042548</v>
+        <v>-0.15967070243238571</v>
       </c>
       <c r="G27">
-        <v>-0.13382693702206641</v>
+        <v>-0.1412756359368397</v>
       </c>
       <c r="H27">
-        <v>-6.248963877778789E-2</v>
+        <v>-6.7576830622424713E-2</v>
       </c>
       <c r="I27">
-        <v>-5.8582728689998441E-2</v>
+        <v>-6.1966982595869982E-2</v>
       </c>
       <c r="J27">
-        <v>-0.13922330535814989</v>
+        <v>-0.13841242502987469</v>
       </c>
       <c r="K27">
-        <v>-0.2254986048242883</v>
+        <v>-0.22600311736729159</v>
       </c>
       <c r="L27">
-        <v>-0.29214512681864818</v>
+        <v>-0.29171910319469901</v>
       </c>
       <c r="M27">
-        <v>-0.3725405050998461</v>
+        <v>-0.35214812360481879</v>
       </c>
       <c r="N27">
-        <v>-0.29761437262308388</v>
+        <v>-0.28041367642717829</v>
       </c>
       <c r="O27">
-        <v>-0.39301742912692661</v>
+        <v>-0.37822942852032748</v>
       </c>
       <c r="P27">
-        <v>-0.43178517072798189</v>
+        <v>-0.41731626433628061</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -1965,49 +1920,49 @@
         <v>42</v>
       </c>
       <c r="B28">
-        <v>0.53871739028441401</v>
+        <v>0.53764249568630307</v>
       </c>
       <c r="C28">
-        <v>0.60375385039156748</v>
+        <v>0.60300762523922768</v>
       </c>
       <c r="D28">
-        <v>0.6404126820360263</v>
+        <v>0.63810567966071008</v>
       </c>
       <c r="E28">
-        <v>0.66410790573211154</v>
+        <v>0.66337350103404746</v>
       </c>
       <c r="F28">
-        <v>0.6351955197488951</v>
+        <v>0.63405121020682365</v>
       </c>
       <c r="G28">
-        <v>0.62010700255556594</v>
+        <v>0.6222558463123733</v>
       </c>
       <c r="H28">
-        <v>0.62170823543318865</v>
+        <v>0.61907802399061274</v>
       </c>
       <c r="I28">
-        <v>0.59845387884238932</v>
+        <v>0.60388045054354567</v>
       </c>
       <c r="J28">
-        <v>0.63757953253652255</v>
+        <v>0.63867556542704851</v>
       </c>
       <c r="K28">
-        <v>0.65435967601516076</v>
+        <v>0.65823530441312239</v>
       </c>
       <c r="L28">
-        <v>0.62332673407591921</v>
+        <v>0.6237605134669717</v>
       </c>
       <c r="M28">
-        <v>0.60638582739859292</v>
+        <v>0.60357910833741046</v>
       </c>
       <c r="N28">
-        <v>0.57319857645498862</v>
+        <v>0.57154647203711773</v>
       </c>
       <c r="O28">
-        <v>0.55136138578645411</v>
+        <v>0.55029852239743349</v>
       </c>
       <c r="P28">
-        <v>0.5053098420152764</v>
+        <v>0.50844667484834372</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2015,49 +1970,49 @@
         <v>43</v>
       </c>
       <c r="B29">
-        <v>0.53926101947645155</v>
+        <v>0.53640501969873267</v>
       </c>
       <c r="C29">
-        <v>0.60782800042608076</v>
+        <v>0.60449557833617318</v>
       </c>
       <c r="D29">
-        <v>0.65312923243949816</v>
+        <v>0.65165626243910213</v>
       </c>
       <c r="E29">
-        <v>0.68699793217901206</v>
+        <v>0.68469643711004613</v>
       </c>
       <c r="F29">
-        <v>0.67693716505460133</v>
+        <v>0.6774606094355865</v>
       </c>
       <c r="G29">
-        <v>0.69173653835947535</v>
+        <v>0.69000245891586509</v>
       </c>
       <c r="H29">
-        <v>0.68479522649919888</v>
+        <v>0.68400800667691164</v>
       </c>
       <c r="I29">
-        <v>0.67495753509203826</v>
-      </c>
-      <c r="J29" s="2">
-        <v>0.71101121403659928</v>
+        <v>0.67428261608935181</v>
+      </c>
+      <c r="J29">
+        <v>0.71151874273345783</v>
       </c>
       <c r="K29">
-        <v>0.71019180921359082</v>
+        <v>0.71001028536625155</v>
       </c>
       <c r="L29">
-        <v>0.71249478641562936</v>
+        <v>0.71073235553634562</v>
       </c>
       <c r="M29">
-        <v>0.70086350689526689</v>
+        <v>0.69685545988120523</v>
       </c>
       <c r="N29">
-        <v>0.68330539171207538</v>
+        <v>0.6797901466876739</v>
       </c>
       <c r="O29">
-        <v>0.66001712877780239</v>
+        <v>0.65552569570001762</v>
       </c>
       <c r="P29">
-        <v>0.62754295127158044</v>
+        <v>0.62176336988606318</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2065,49 +2020,49 @@
         <v>44</v>
       </c>
       <c r="B30">
-        <v>0.55238158570826057</v>
+        <v>0.55261419036347614</v>
       </c>
       <c r="C30">
-        <v>0.58810286180893112</v>
+        <v>0.58729817697553022</v>
       </c>
       <c r="D30">
-        <v>0.62721002647843294</v>
+        <v>0.62649135357069707</v>
       </c>
       <c r="E30">
-        <v>0.65298783454132425</v>
+        <v>0.65325144659820766</v>
       </c>
       <c r="F30">
-        <v>0.63214277404981334</v>
+        <v>0.63513690082954777</v>
       </c>
       <c r="G30">
-        <v>0.65336554034226912</v>
+        <v>0.65428835054863688</v>
       </c>
       <c r="H30">
-        <v>0.64119359767572282</v>
+        <v>0.64358591556897626</v>
       </c>
       <c r="I30">
-        <v>0.6436764382994008</v>
+        <v>0.63716105489957975</v>
       </c>
       <c r="J30">
-        <v>0.64461230180638207</v>
+        <v>0.64325299926513435</v>
       </c>
       <c r="K30">
-        <v>0.66224242075718565</v>
+        <v>0.66384424717051482</v>
       </c>
       <c r="L30">
-        <v>0.65607370149890132</v>
+        <v>0.65420399928641026</v>
       </c>
       <c r="M30">
-        <v>0.65239560516709894</v>
+        <v>0.65120673138108709</v>
       </c>
       <c r="N30">
-        <v>0.63181717368005619</v>
+        <v>0.62675121614276796</v>
       </c>
       <c r="O30">
-        <v>0.59788678909852133</v>
+        <v>0.59329339582405605</v>
       </c>
       <c r="P30">
-        <v>0.5616952831445724</v>
+        <v>0.55497656606051893</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2115,49 +2070,49 @@
         <v>45</v>
       </c>
       <c r="B31">
-        <v>0.55524121445705876</v>
+        <v>0.55395937000236062</v>
       </c>
       <c r="C31">
-        <v>0.59080164247310063</v>
+        <v>0.58966516266318203</v>
       </c>
       <c r="D31">
-        <v>0.63061340645345054</v>
+        <v>0.63031215435078125</v>
       </c>
       <c r="E31">
-        <v>0.65579169473160193</v>
+        <v>0.65498780850518701</v>
       </c>
       <c r="F31">
-        <v>0.63652387357994977</v>
+        <v>0.63713754866504135</v>
       </c>
       <c r="G31">
-        <v>0.65362968905934826</v>
+        <v>0.65428100772031728</v>
       </c>
       <c r="H31">
-        <v>0.64294781609286011</v>
+        <v>0.64564531390126456</v>
       </c>
       <c r="I31">
-        <v>0.63779730088608777</v>
+        <v>0.63893349804073074</v>
       </c>
       <c r="J31">
-        <v>0.63091841300656748</v>
+        <v>0.63129883772732809</v>
       </c>
       <c r="K31">
-        <v>0.63563561848522288</v>
+        <v>0.63598297324612352</v>
       </c>
       <c r="L31">
-        <v>0.63416126511789872</v>
+        <v>0.6335405713586465</v>
       </c>
       <c r="M31">
-        <v>0.63478439594626201</v>
+        <v>0.63673720254380262</v>
       </c>
       <c r="N31">
-        <v>0.62283073249152854</v>
+        <v>0.62825234098003357</v>
       </c>
       <c r="O31">
-        <v>0.60209896290955001</v>
+        <v>0.60685576226673477</v>
       </c>
       <c r="P31">
-        <v>0.61046896842197695</v>
+        <v>0.61576750057649943</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -2165,49 +2120,49 @@
         <v>46</v>
       </c>
       <c r="B32">
-        <v>0.5379145393060405</v>
+        <v>0.53715974804411426</v>
       </c>
       <c r="C32">
-        <v>0.60678488076898585</v>
+        <v>0.60532508889636683</v>
       </c>
       <c r="D32">
-        <v>0.65056836324701561</v>
+        <v>0.65039773168920356</v>
       </c>
       <c r="E32">
-        <v>0.68335576417178001</v>
+        <v>0.68398026907034282</v>
       </c>
       <c r="F32">
-        <v>0.67395831061716116</v>
+        <v>0.67299186974523817</v>
       </c>
       <c r="G32">
-        <v>0.68402843777379563</v>
+        <v>0.682992630704506</v>
       </c>
       <c r="H32">
-        <v>0.67755450065913769</v>
+        <v>0.67817102287333531</v>
       </c>
       <c r="I32">
-        <v>0.65662470657997707</v>
+        <v>0.65344240839786483</v>
       </c>
       <c r="J32">
-        <v>0.68670100977229553</v>
+        <v>0.6826207362636274</v>
       </c>
       <c r="K32">
-        <v>0.69211896825893948</v>
+        <v>0.68736955406188727</v>
       </c>
       <c r="L32">
-        <v>0.70147692639131964</v>
+        <v>0.69517679590895631</v>
       </c>
       <c r="M32">
-        <v>0.69632538766293328</v>
+        <v>0.6896447982648134</v>
       </c>
       <c r="N32">
-        <v>0.68201926942648394</v>
+        <v>0.6737536369169187</v>
       </c>
       <c r="O32">
-        <v>0.67176070175859059</v>
+        <v>0.66249627896120711</v>
       </c>
       <c r="P32">
-        <v>0.63706254321837463</v>
+        <v>0.62520012693425753</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -2215,49 +2170,49 @@
         <v>47</v>
       </c>
       <c r="B33">
-        <v>0.53536148285623908</v>
+        <v>0.53763870974136874</v>
       </c>
       <c r="C33">
-        <v>0.60358330031733232</v>
+        <v>0.60583665350687066</v>
       </c>
       <c r="D33">
-        <v>0.64976608863597851</v>
+        <v>0.65192067640341778</v>
       </c>
       <c r="E33">
-        <v>0.68277386390075445</v>
+        <v>0.68458883975270401</v>
       </c>
       <c r="F33">
-        <v>0.67615275110608064</v>
+        <v>0.67482936777830838</v>
       </c>
       <c r="G33">
-        <v>0.68597261334438719</v>
+        <v>0.68374799252797336</v>
       </c>
       <c r="H33">
-        <v>0.68197436278355716</v>
+        <v>0.67885347106138516</v>
       </c>
       <c r="I33">
-        <v>0.66078894955731393</v>
+        <v>0.65497964859637026</v>
       </c>
       <c r="J33">
-        <v>0.69004279147161685</v>
+        <v>0.69070443262393622</v>
       </c>
       <c r="K33">
-        <v>0.69385086692065034</v>
+        <v>0.69118212479926899</v>
       </c>
       <c r="L33">
-        <v>0.70076116393474408</v>
+        <v>0.70126385664153856</v>
       </c>
       <c r="M33">
-        <v>0.69479774365628688</v>
+        <v>0.69296958320835611</v>
       </c>
       <c r="N33">
-        <v>0.68004186572542413</v>
+        <v>0.67787979303906698</v>
       </c>
       <c r="O33">
-        <v>0.66412214959897087</v>
+        <v>0.66173613501862338</v>
       </c>
       <c r="P33">
-        <v>0.62136546915923063</v>
+        <v>0.62360953332997704</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -2265,49 +2220,49 @@
         <v>48</v>
       </c>
       <c r="B34">
-        <v>0.53744329261821422</v>
+        <v>0.5371701134534127</v>
       </c>
       <c r="C34">
-        <v>0.60616636145010472</v>
+        <v>0.60553124781495105</v>
       </c>
       <c r="D34">
-        <v>0.6516353914490528</v>
+        <v>0.65142564582459817</v>
       </c>
       <c r="E34">
-        <v>0.68461704996205452</v>
+        <v>0.68433494367609538</v>
       </c>
       <c r="F34">
-        <v>0.6753365421101547</v>
+        <v>0.67450668657063073</v>
       </c>
       <c r="G34">
-        <v>0.68472026931862362</v>
+        <v>0.68659565320418958</v>
       </c>
       <c r="H34">
-        <v>0.6787793954039566</v>
+        <v>0.68032026294405656</v>
       </c>
       <c r="I34">
-        <v>0.65247187237415194</v>
+        <v>0.6564205059461774</v>
       </c>
       <c r="J34">
-        <v>0.68696588949986348</v>
+        <v>0.68626163282254404</v>
       </c>
       <c r="K34">
-        <v>0.69151847110326092</v>
+        <v>0.69408613475919156</v>
       </c>
       <c r="L34">
-        <v>0.70193810186453054</v>
+        <v>0.7045663376125868</v>
       </c>
       <c r="M34">
-        <v>0.69424512682676787</v>
+        <v>0.69701526781314693</v>
       </c>
       <c r="N34">
-        <v>0.67912176273377445</v>
+        <v>0.67911056560695249</v>
       </c>
       <c r="O34">
-        <v>0.66887598393061665</v>
+        <v>0.66860881045819798</v>
       </c>
       <c r="P34">
-        <v>0.63087107599244696</v>
+        <v>0.62807741521494032</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -2315,49 +2270,49 @@
         <v>49</v>
       </c>
       <c r="B35">
-        <v>0.53576377202913583</v>
+        <v>0.5371442764375467</v>
       </c>
       <c r="C35">
-        <v>0.60472699505755456</v>
+        <v>0.60558759206344648</v>
       </c>
       <c r="D35">
-        <v>0.64998871118045798</v>
+        <v>0.65040884292295331</v>
       </c>
       <c r="E35">
-        <v>0.6845815503551882</v>
+        <v>0.68471137442880259</v>
       </c>
       <c r="F35">
-        <v>0.67658678790257054</v>
+        <v>0.67637843174079881</v>
       </c>
       <c r="G35">
-        <v>0.68554244337073644</v>
+        <v>0.68645692274414327</v>
       </c>
       <c r="H35">
-        <v>0.67895522847713574</v>
+        <v>0.68036347732204416</v>
       </c>
       <c r="I35">
-        <v>0.65494586962263301</v>
+        <v>0.65602116476057204</v>
       </c>
       <c r="J35">
-        <v>0.68791284535114461</v>
+        <v>0.68869106243119038</v>
       </c>
       <c r="K35">
-        <v>0.69183253033312309</v>
+        <v>0.69234628378132079</v>
       </c>
       <c r="L35">
-        <v>0.70482272037367977</v>
+        <v>0.70347113652831328</v>
       </c>
       <c r="M35">
-        <v>0.69719125434245521</v>
+        <v>0.69717462158805599</v>
       </c>
       <c r="N35">
-        <v>0.68418087215779089</v>
+        <v>0.68307551659357579</v>
       </c>
       <c r="O35">
-        <v>0.67829862392157303</v>
+        <v>0.6710724974340434</v>
       </c>
       <c r="P35">
-        <v>0.64449621250591516</v>
+        <v>0.63378701230227508</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -2365,49 +2320,49 @@
         <v>50</v>
       </c>
       <c r="B36">
-        <v>0.53750804627819038</v>
+        <v>0.53689545812799222</v>
       </c>
       <c r="C36">
-        <v>0.60610804354142822</v>
+        <v>0.60643796398459027</v>
       </c>
       <c r="D36">
-        <v>0.65279962613083409</v>
+        <v>0.65161474324001278</v>
       </c>
       <c r="E36">
-        <v>0.68545894462201939</v>
+        <v>0.68444126177669906</v>
       </c>
       <c r="F36">
-        <v>0.67536318059984457</v>
+        <v>0.67759222500955685</v>
       </c>
       <c r="G36">
-        <v>0.68744754274952424</v>
+        <v>0.68750280480122239</v>
       </c>
       <c r="H36">
-        <v>0.67845492686592002</v>
+        <v>0.68119476749380081</v>
       </c>
       <c r="I36">
-        <v>0.65819691184803886</v>
+        <v>0.6627127615216506</v>
       </c>
       <c r="J36">
-        <v>0.68772572360891704</v>
+        <v>0.69138577950329971</v>
       </c>
       <c r="K36">
-        <v>0.69041524847951075</v>
+        <v>0.6915586468319459</v>
       </c>
       <c r="L36">
-        <v>0.69336295546355198</v>
+        <v>0.69443924062252171</v>
       </c>
       <c r="M36">
-        <v>0.68422507750076322</v>
+        <v>0.6883498123640388</v>
       </c>
       <c r="N36">
-        <v>0.67143436933290968</v>
+        <v>0.67124680072961951</v>
       </c>
       <c r="O36">
-        <v>0.6629166748155727</v>
+        <v>0.66499396612834194</v>
       </c>
       <c r="P36">
-        <v>0.6292763976631951</v>
+        <v>0.63043301826988196</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -2415,49 +2370,49 @@
         <v>51</v>
       </c>
       <c r="B37">
-        <v>0.53410322700136603</v>
+        <v>0.53590968593451738</v>
       </c>
       <c r="C37">
-        <v>0.6035741660047883</v>
+        <v>0.60437776810114185</v>
       </c>
       <c r="D37">
-        <v>0.64908503821864605</v>
+        <v>0.65187333165990469</v>
       </c>
       <c r="E37">
-        <v>0.68257933023361506</v>
+        <v>0.68521103588555077</v>
       </c>
       <c r="F37">
-        <v>0.67252782484759732</v>
+        <v>0.67607370404604261</v>
       </c>
       <c r="G37">
-        <v>0.68204437363451709</v>
+        <v>0.68652192700655568</v>
       </c>
       <c r="H37">
-        <v>0.67577287744906911</v>
+        <v>0.6821830256698117</v>
       </c>
       <c r="I37">
-        <v>0.65672672961351142</v>
+        <v>0.65866623618627629</v>
       </c>
       <c r="J37">
-        <v>0.68696722454935377</v>
+        <v>0.68875987913877346</v>
       </c>
       <c r="K37">
-        <v>0.68579169750331104</v>
+        <v>0.68881340472996877</v>
       </c>
       <c r="L37">
-        <v>0.69244507386195753</v>
+        <v>0.69420918277593924</v>
       </c>
       <c r="M37">
-        <v>0.68525931665804674</v>
+        <v>0.68626574623867442</v>
       </c>
       <c r="N37">
-        <v>0.67301729111799691</v>
+        <v>0.66904416451891335</v>
       </c>
       <c r="O37">
-        <v>0.66451333912208388</v>
+        <v>0.65773930081617593</v>
       </c>
       <c r="P37">
-        <v>0.62737897273940046</v>
+        <v>0.62279080265227937</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -2465,49 +2420,49 @@
         <v>52</v>
       </c>
       <c r="B38">
-        <v>0.53717829859723198</v>
+        <v>0.5373286562186167</v>
       </c>
       <c r="C38">
-        <v>0.60576863081711785</v>
+        <v>0.60658865244109395</v>
       </c>
       <c r="D38">
-        <v>0.65217415884593422</v>
+        <v>0.65184232280944976</v>
       </c>
       <c r="E38">
-        <v>0.68562100289276906</v>
+        <v>0.68511399889041635</v>
       </c>
       <c r="F38">
-        <v>0.67708820153415294</v>
+        <v>0.67483231125327259</v>
       </c>
       <c r="G38">
-        <v>0.68851547611084707</v>
+        <v>0.68556522660131369</v>
       </c>
       <c r="H38">
-        <v>0.68018964806739102</v>
+        <v>0.67946633796587663</v>
       </c>
       <c r="I38">
-        <v>0.66349787803591709</v>
+        <v>0.66070936105043598</v>
       </c>
       <c r="J38">
-        <v>0.68980249400497673</v>
+        <v>0.68888450519631494</v>
       </c>
       <c r="K38">
-        <v>0.69511590653658095</v>
+        <v>0.68990287198779909</v>
       </c>
       <c r="L38">
-        <v>0.69696801113255435</v>
+        <v>0.69511268837556184</v>
       </c>
       <c r="M38">
-        <v>0.6933553114701908</v>
+        <v>0.69131429391794674</v>
       </c>
       <c r="N38">
-        <v>0.67962525341009572</v>
+        <v>0.67638212336803027</v>
       </c>
       <c r="O38">
-        <v>0.66836647610498379</v>
+        <v>0.66779228720198558</v>
       </c>
       <c r="P38">
-        <v>0.62991006116697501</v>
+        <v>0.62160397156593017</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -2515,49 +2470,49 @@
         <v>53</v>
       </c>
       <c r="B39">
-        <v>0.53610112566814372</v>
+        <v>0.53791013612636096</v>
       </c>
       <c r="C39">
-        <v>0.6041772602767751</v>
+        <v>0.60610467211816088</v>
       </c>
       <c r="D39">
-        <v>0.64876034377153247</v>
+        <v>0.65343225951851935</v>
       </c>
       <c r="E39">
-        <v>0.68369162820151053</v>
+        <v>0.68652668240401404</v>
       </c>
       <c r="F39">
-        <v>0.67373312302028654</v>
+        <v>0.67726021612038745</v>
       </c>
       <c r="G39">
-        <v>0.68339574477732934</v>
+        <v>0.6888988401411702</v>
       </c>
       <c r="H39">
-        <v>0.67811987956860831</v>
+        <v>0.67994716667953747</v>
       </c>
       <c r="I39">
-        <v>0.65538268923215548</v>
+        <v>0.65843858913999997</v>
       </c>
       <c r="J39">
-        <v>0.68524557644092654</v>
+        <v>0.68966049262317974</v>
       </c>
       <c r="K39">
-        <v>0.6902823946547948</v>
+        <v>0.69137924086432367</v>
       </c>
       <c r="L39">
-        <v>0.69568230999712022</v>
+        <v>0.69603823477206461</v>
       </c>
       <c r="M39">
-        <v>0.69051160619169583</v>
+        <v>0.6901555295573657</v>
       </c>
       <c r="N39">
-        <v>0.67611368317626008</v>
+        <v>0.67884221581999893</v>
       </c>
       <c r="O39">
-        <v>0.67078958326207538</v>
+        <v>0.6650567662359359</v>
       </c>
       <c r="P39">
-        <v>0.63261197724239615</v>
+        <v>0.62383529598082343</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -2565,49 +2520,49 @@
         <v>54</v>
       </c>
       <c r="B40">
-        <v>0.53579839388389949</v>
+        <v>0.53793247554654589</v>
       </c>
       <c r="C40">
-        <v>0.60578733206898183</v>
+        <v>0.60615132508926983</v>
       </c>
       <c r="D40">
-        <v>0.65236388648531662</v>
+        <v>0.65002795780373757</v>
       </c>
       <c r="E40">
-        <v>0.6859473383659962</v>
+        <v>0.68362771793247534</v>
       </c>
       <c r="F40">
-        <v>0.67836176180555752</v>
+        <v>0.67365531859542738</v>
       </c>
       <c r="G40">
-        <v>0.68740367498841093</v>
+        <v>0.6830479848619242</v>
       </c>
       <c r="H40">
-        <v>0.68047451885977039</v>
+        <v>0.67657431550782221</v>
       </c>
       <c r="I40">
-        <v>0.65973321624646619</v>
+        <v>0.65084853501762563</v>
       </c>
       <c r="J40">
-        <v>0.69113816174133802</v>
+        <v>0.68478122013357734</v>
       </c>
       <c r="K40">
-        <v>0.69181948827256967</v>
+        <v>0.68846893386077301</v>
       </c>
       <c r="L40">
-        <v>0.70367270879990218</v>
+        <v>0.70118579107292744</v>
       </c>
       <c r="M40">
-        <v>0.69647361754922521</v>
+        <v>0.6934407159213184</v>
       </c>
       <c r="N40">
-        <v>0.68320661287963247</v>
+        <v>0.68048523752501278</v>
       </c>
       <c r="O40">
-        <v>0.67492135771598982</v>
+        <v>0.67400157301244834</v>
       </c>
       <c r="P40">
-        <v>0.63206102231193129</v>
+        <v>0.63349883813130914</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -2615,49 +2570,49 @@
         <v>55</v>
       </c>
       <c r="B41">
-        <v>0.5556732878396381</v>
+        <v>0.55550493726214845</v>
       </c>
       <c r="C41">
-        <v>0.61573388040975474</v>
+        <v>0.61921413031763006</v>
       </c>
       <c r="D41">
-        <v>0.67203497772826903</v>
+        <v>0.6759544923668539</v>
       </c>
       <c r="E41">
-        <v>0.66314026114755353</v>
+        <v>0.66737241242795498</v>
       </c>
       <c r="F41">
-        <v>0.62841772921461947</v>
+        <v>0.63406121573267815</v>
       </c>
       <c r="G41">
-        <v>0.56681899964708249</v>
+        <v>0.57698601339105526</v>
       </c>
       <c r="H41">
-        <v>0.57419252175664726</v>
+        <v>0.5863546254861618</v>
       </c>
       <c r="I41">
-        <v>0.55932511327306178</v>
+        <v>0.56853694481168982</v>
       </c>
       <c r="J41">
-        <v>0.54245419385171234</v>
+        <v>0.55220103171711699</v>
       </c>
       <c r="K41">
-        <v>0.54737744611177575</v>
+        <v>0.55405339812545307</v>
       </c>
       <c r="L41">
-        <v>0.52344638191927262</v>
+        <v>0.53377919786722272</v>
       </c>
       <c r="M41">
-        <v>0.52549999808339409</v>
+        <v>0.53423320745651548</v>
       </c>
       <c r="N41">
-        <v>0.50873082846985618</v>
+        <v>0.51814383781822548</v>
       </c>
       <c r="O41">
-        <v>0.49119239625053301</v>
+        <v>0.49920394176560889</v>
       </c>
       <c r="P41">
-        <v>0.48245735146626462</v>
+        <v>0.48786712940817539</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -2665,49 +2620,49 @@
         <v>56</v>
       </c>
       <c r="B42">
-        <v>0.55741614169897025</v>
+        <v>0.5571894147221913</v>
       </c>
       <c r="C42">
-        <v>0.62955092824314129</v>
+        <v>0.62403933170222248</v>
       </c>
       <c r="D42">
-        <v>0.68230973874962342</v>
+        <v>0.67812511990570234</v>
       </c>
       <c r="E42">
-        <v>0.67673303643029137</v>
+        <v>0.67118547195871525</v>
       </c>
       <c r="F42">
-        <v>0.63841711734812401</v>
+        <v>0.63394529487125129</v>
       </c>
       <c r="G42">
-        <v>0.59198362797897675</v>
+        <v>0.58566694379866757</v>
       </c>
       <c r="H42">
-        <v>0.61714378024967154</v>
+        <v>0.61647175172830893</v>
       </c>
       <c r="I42">
-        <v>0.61181308526954248</v>
+        <v>0.60848127286810838</v>
       </c>
       <c r="J42">
-        <v>0.62786834760799415</v>
+        <v>0.62600605925763586</v>
       </c>
       <c r="K42">
-        <v>0.65050057858044663</v>
+        <v>0.65252517901111573</v>
       </c>
       <c r="L42">
-        <v>0.6424028930775213</v>
+        <v>0.64170540338511894</v>
       </c>
       <c r="M42">
-        <v>0.63034107419528962</v>
+        <v>0.63158390866027814</v>
       </c>
       <c r="N42">
-        <v>0.63081903336385914</v>
+        <v>0.63364463865013054</v>
       </c>
       <c r="O42">
-        <v>0.61197067736706579</v>
+        <v>0.61646655676683737</v>
       </c>
       <c r="P42">
-        <v>0.57563305061754977</v>
+        <v>0.57846870707577835</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -2715,49 +2670,49 @@
         <v>57</v>
       </c>
       <c r="B43">
-        <v>0.55911921557017519</v>
+        <v>0.5567449878947881</v>
       </c>
       <c r="C43">
-        <v>0.62590166085847587</v>
+        <v>0.62114186751852707</v>
       </c>
       <c r="D43">
-        <v>0.68071831546511585</v>
+        <v>0.67652155098045963</v>
       </c>
       <c r="E43">
-        <v>0.6729604073803378</v>
+        <v>0.66844094378997165</v>
       </c>
       <c r="F43">
-        <v>0.63720127857851749</v>
+        <v>0.63497646951032993</v>
       </c>
       <c r="G43">
-        <v>0.59191375548976921</v>
+        <v>0.58385771889908589</v>
       </c>
       <c r="H43">
-        <v>0.62175832134221898</v>
+        <v>0.61532314291731049</v>
       </c>
       <c r="I43">
-        <v>0.61593379145714178</v>
+        <v>0.60778134763525626</v>
       </c>
       <c r="J43">
-        <v>0.6250891263069005</v>
+        <v>0.61778526285745372</v>
       </c>
       <c r="K43">
-        <v>0.63619929981815571</v>
+        <v>0.63135651475005183</v>
       </c>
       <c r="L43">
-        <v>0.62880535029110685</v>
+        <v>0.62648864431690965</v>
       </c>
       <c r="M43">
-        <v>0.62167014526604614</v>
+        <v>0.61704274221703048</v>
       </c>
       <c r="N43">
-        <v>0.62888513686540481</v>
+        <v>0.62450306853277471</v>
       </c>
       <c r="O43">
-        <v>0.62246944539564397</v>
+        <v>0.61955105756023721</v>
       </c>
       <c r="P43">
-        <v>0.59709008023942611</v>
+        <v>0.5919103540876165</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -2765,49 +2720,49 @@
         <v>58</v>
       </c>
       <c r="B44">
-        <v>0.51766239465768538</v>
+        <v>0.51818993768802069</v>
       </c>
       <c r="C44">
-        <v>0.50383939601683614</v>
+        <v>0.50343149693115852</v>
       </c>
       <c r="D44">
-        <v>0.56095029785646067</v>
+        <v>0.56053383399257284</v>
       </c>
       <c r="E44">
-        <v>0.60897858772614943</v>
+        <v>0.61140600802542688</v>
       </c>
       <c r="F44">
-        <v>0.6115766267291437</v>
+        <v>0.6174652657910531</v>
       </c>
       <c r="G44">
-        <v>0.61425525324421826</v>
+        <v>0.62186775560155916</v>
       </c>
       <c r="H44">
-        <v>0.59761528620188009</v>
+        <v>0.60285881459982504</v>
       </c>
       <c r="I44">
-        <v>0.59194190699787552</v>
+        <v>0.59855277440842658</v>
       </c>
       <c r="J44">
-        <v>0.58342817947713266</v>
+        <v>0.58884182026598175</v>
       </c>
       <c r="K44">
-        <v>0.55110566010907258</v>
+        <v>0.55592724831584983</v>
       </c>
       <c r="L44">
-        <v>0.51461214552036971</v>
+        <v>0.5195299951164748</v>
       </c>
       <c r="M44">
-        <v>0.48434170520146569</v>
+        <v>0.48990532306480328</v>
       </c>
       <c r="N44">
-        <v>0.45682443547423618</v>
+        <v>0.4616592370555393</v>
       </c>
       <c r="O44">
-        <v>0.42708603298714709</v>
+        <v>0.43186043217522219</v>
       </c>
       <c r="P44">
-        <v>0.37898834712517859</v>
+        <v>0.38132760445014302</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -2815,49 +2770,49 @@
         <v>59</v>
       </c>
       <c r="B45">
-        <v>0.50668482261183601</v>
+        <v>0.50818896628040922</v>
       </c>
       <c r="C45">
-        <v>0.54649519820391002</v>
+        <v>0.54657360083707052</v>
       </c>
       <c r="D45">
-        <v>0.52989336840915557</v>
+        <v>0.53034973573516475</v>
       </c>
       <c r="E45">
-        <v>0.49849676127612358</v>
+        <v>0.49904642736018529</v>
       </c>
       <c r="F45">
-        <v>0.45134211559637549</v>
+        <v>0.45551228853409109</v>
       </c>
       <c r="G45">
-        <v>0.42290627544334419</v>
+        <v>0.43628773498789192</v>
       </c>
       <c r="H45">
-        <v>0.43112230680239078</v>
+        <v>0.4437640302740552</v>
       </c>
       <c r="I45">
-        <v>0.44150251099345528</v>
+        <v>0.44826256989585372</v>
       </c>
       <c r="J45">
-        <v>0.43037430699059143</v>
+        <v>0.43702410430934252</v>
       </c>
       <c r="K45">
-        <v>0.35651643440291308</v>
+        <v>0.36434384439770801</v>
       </c>
       <c r="L45">
-        <v>0.30099619595476829</v>
+        <v>0.30303189485004062</v>
       </c>
       <c r="M45">
-        <v>0.2734964114034415</v>
+        <v>0.27375110458232982</v>
       </c>
       <c r="N45">
-        <v>0.22170676884091889</v>
+        <v>0.21720869396933079</v>
       </c>
       <c r="O45">
-        <v>0.19729901650032869</v>
+        <v>0.19062667465035549</v>
       </c>
       <c r="P45">
-        <v>0.221053556967516</v>
+        <v>0.21107025411203459</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -2865,49 +2820,49 @@
         <v>60</v>
       </c>
       <c r="B46">
-        <v>0.41458397246306822</v>
+        <v>0.41564541635567231</v>
       </c>
       <c r="C46">
-        <v>0.52686208705528803</v>
+        <v>0.52794463695948901</v>
       </c>
       <c r="D46">
-        <v>0.51868514659670328</v>
+        <v>0.5262297862251607</v>
       </c>
       <c r="E46">
-        <v>0.52372289933354799</v>
+        <v>0.52733212668426066</v>
       </c>
       <c r="F46">
-        <v>0.45861429257995451</v>
+        <v>0.46905732986448739</v>
       </c>
       <c r="G46">
-        <v>0.47448914663984709</v>
+        <v>0.48261748596722681</v>
       </c>
       <c r="H46">
-        <v>0.47723494329869548</v>
+        <v>0.48340494641242082</v>
       </c>
       <c r="I46">
-        <v>0.42792123207390781</v>
+        <v>0.43959557811508171</v>
       </c>
       <c r="J46">
-        <v>0.35035570892882212</v>
+        <v>0.36739561054141362</v>
       </c>
       <c r="K46">
-        <v>0.27690471800405381</v>
+        <v>0.29686349739613899</v>
       </c>
       <c r="L46">
-        <v>0.2609810777527703</v>
+        <v>0.27531122259186042</v>
       </c>
       <c r="M46">
-        <v>0.25218322012300748</v>
+        <v>0.26913943820960728</v>
       </c>
       <c r="N46">
-        <v>0.22535360208437791</v>
+        <v>0.24383457465642011</v>
       </c>
       <c r="O46">
-        <v>0.21074295636121379</v>
+        <v>0.22865838251651599</v>
       </c>
       <c r="P46">
-        <v>0.21216077146512261</v>
+        <v>0.23312820607189499</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -2915,54 +2870,54 @@
         <v>61</v>
       </c>
       <c r="B47">
-        <v>0.53093155293912553</v>
+        <v>0.52806500155134972</v>
       </c>
       <c r="C47">
-        <v>0.5226216515082186</v>
+        <v>0.5170487152013612</v>
       </c>
       <c r="D47">
-        <v>0.51301906217236726</v>
+        <v>0.50361264985950815</v>
       </c>
       <c r="E47">
-        <v>0.49223294650654331</v>
+        <v>0.47943856368576387</v>
       </c>
       <c r="F47">
-        <v>0.41640956975605292</v>
+        <v>0.40432536799439928</v>
       </c>
       <c r="G47">
-        <v>0.4475073743155048</v>
+        <v>0.43106732420256899</v>
       </c>
       <c r="H47">
-        <v>0.46082951608996692</v>
+        <v>0.45479994926881601</v>
       </c>
       <c r="I47">
-        <v>0.48412098751127081</v>
+        <v>0.47099834829240922</v>
       </c>
       <c r="J47">
-        <v>0.42358904412169301</v>
+        <v>0.40712128474174308</v>
       </c>
       <c r="K47">
-        <v>0.42767925455060402</v>
+        <v>0.40858693773966859</v>
       </c>
       <c r="L47">
-        <v>0.39332127106700893</v>
+        <v>0.37279023256144622</v>
       </c>
       <c r="M47">
-        <v>0.37823293192051088</v>
+        <v>0.3557505069269522</v>
       </c>
       <c r="N47">
-        <v>0.38138420990844812</v>
+        <v>0.36368329642042252</v>
       </c>
       <c r="O47">
-        <v>0.38219081779486908</v>
+        <v>0.36558029668146907</v>
       </c>
       <c r="P47">
-        <v>0.3808552635458185</v>
+        <v>0.36504565916542348</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P28 B30:P47 B29:K29 M29:P29">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="B2:P47">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2972,7 +2927,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_ADJR2.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\total.trans.carotenes.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_ADJR2</t>
-  </si>
-  <si>
-    <t>LV2_ADJR2</t>
-  </si>
-  <si>
-    <t>LV3_ADJR2</t>
-  </si>
-  <si>
-    <t>LV4_ADJR2</t>
-  </si>
-  <si>
-    <t>LV5_ADJR2</t>
-  </si>
-  <si>
-    <t>LV6_ADJR2</t>
-  </si>
-  <si>
-    <t>LV7_ADJR2</t>
-  </si>
-  <si>
-    <t>LV8_ADJR2</t>
-  </si>
-  <si>
-    <t>LV9_ADJR2</t>
-  </si>
-  <si>
-    <t>LV10_ADJR2</t>
-  </si>
-  <si>
-    <t>LV11_ADJR2</t>
-  </si>
-  <si>
-    <t>LV12_ADJR2</t>
-  </si>
-  <si>
-    <t>LV13_ADJR2</t>
-  </si>
-  <si>
-    <t>LV14_ADJR2</t>
-  </si>
-  <si>
-    <t>LV15_ADJR2</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,19 +63,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -313,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -345,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -380,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -556,2378 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_ADJR2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_ADJR2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_ADJR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_ADJR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_ADJR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_ADJR2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_ADJR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_ADJR2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_ADJR2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_ADJR2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_ADJR2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_ADJR2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_ADJR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_ADJR2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_ADJR2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_ADJR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>0.33752746789113541</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>0.50127267550258181</v>
+        <v>0.3401923007812775</v>
       </c>
       <c r="D2">
-        <v>0.53689770103449874</v>
+        <v>0.5039696220618363</v>
       </c>
       <c r="E2">
-        <v>0.57902586480973928</v>
+        <v>0.5389334429152268</v>
       </c>
       <c r="F2">
-        <v>0.58824853999709781</v>
+        <v>0.5804433350163597</v>
       </c>
       <c r="G2">
-        <v>0.61311523553293712</v>
+        <v>0.591701028337686</v>
       </c>
       <c r="H2">
-        <v>0.62055598102525922</v>
+        <v>0.6176851233369133</v>
       </c>
       <c r="I2">
-        <v>0.6090200881278659</v>
+        <v>0.6246392930079072</v>
       </c>
       <c r="J2">
-        <v>0.58339830542813975</v>
+        <v>0.6133573244366171</v>
       </c>
       <c r="K2">
-        <v>0.5543053785561084</v>
+        <v>0.5885547824158983</v>
       </c>
       <c r="L2">
-        <v>0.56313154247447406</v>
+        <v>0.5589244971796311</v>
       </c>
       <c r="M2">
-        <v>0.52297644828172607</v>
+        <v>0.5639095246958097</v>
       </c>
       <c r="N2">
-        <v>0.49609067029620663</v>
+        <v>0.5269256820339188</v>
       </c>
       <c r="O2">
-        <v>0.49582942369890759</v>
+        <v>0.499545890642749</v>
       </c>
       <c r="P2">
-        <v>0.51401101628864809</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.5031845588205035</v>
+      </c>
+      <c r="Q2">
+        <v>0.5201852689576251</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>0.41957734669781721</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>0.51882981661691896</v>
+        <v>0.4167253425994269</v>
       </c>
       <c r="D3">
-        <v>0.52525713359456461</v>
+        <v>0.5149456145039087</v>
       </c>
       <c r="E3">
-        <v>0.52471288598069621</v>
+        <v>0.5199973655213753</v>
       </c>
       <c r="F3">
-        <v>0.50242334204022165</v>
+        <v>0.5197373499739153</v>
       </c>
       <c r="G3">
-        <v>0.49681484025899281</v>
+        <v>0.4990305645072062</v>
       </c>
       <c r="H3">
-        <v>0.44316694856344929</v>
+        <v>0.4926636670042787</v>
       </c>
       <c r="I3">
-        <v>0.42713803750678758</v>
+        <v>0.442906341517888</v>
       </c>
       <c r="J3">
-        <v>0.40802394286690769</v>
+        <v>0.4275072310538007</v>
       </c>
       <c r="K3">
-        <v>0.41311154281148388</v>
+        <v>0.4086719048627042</v>
       </c>
       <c r="L3">
-        <v>0.39147809451842103</v>
+        <v>0.4166082856172382</v>
       </c>
       <c r="M3">
-        <v>0.32936347104689101</v>
+        <v>0.3943756110582833</v>
       </c>
       <c r="N3">
-        <v>0.26035581498960297</v>
+        <v>0.3329377874269732</v>
       </c>
       <c r="O3">
-        <v>0.20498379476734729</v>
+        <v>0.2676697755179921</v>
       </c>
       <c r="P3">
-        <v>0.14981843114882959</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.2138309413791665</v>
+      </c>
+      <c r="Q3">
+        <v>0.1644246266303695</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>0.35914269094088958</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>0.48696204257489162</v>
+        <v>0.3589760444589701</v>
       </c>
       <c r="D4">
-        <v>0.502426426342509</v>
+        <v>0.4869092359173952</v>
       </c>
       <c r="E4">
-        <v>0.49703148487053889</v>
+        <v>0.5021989870218149</v>
       </c>
       <c r="F4">
-        <v>0.51545882359221773</v>
+        <v>0.493169706568005</v>
       </c>
       <c r="G4">
-        <v>0.53758854317164051</v>
+        <v>0.5119307846378091</v>
       </c>
       <c r="H4">
-        <v>0.56108385790689608</v>
+        <v>0.533377726289344</v>
       </c>
       <c r="I4">
-        <v>0.54039283716011477</v>
+        <v>0.5630740498320163</v>
       </c>
       <c r="J4">
-        <v>0.51609148556110185</v>
+        <v>0.5400152534582788</v>
       </c>
       <c r="K4">
-        <v>0.44820647138381942</v>
+        <v>0.5176054521160223</v>
       </c>
       <c r="L4">
-        <v>0.43277455334644638</v>
+        <v>0.4517522278345056</v>
       </c>
       <c r="M4">
-        <v>0.46290229421563839</v>
+        <v>0.4331391953995471</v>
       </c>
       <c r="N4">
-        <v>0.46757651821857782</v>
+        <v>0.4658765075540052</v>
       </c>
       <c r="O4">
-        <v>0.45806175907763219</v>
+        <v>0.4752271164518779</v>
       </c>
       <c r="P4">
-        <v>0.46015117531830479</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.4645094752489701</v>
+      </c>
+      <c r="Q4">
+        <v>0.470689810756662</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>0.50957378081247262</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>0.51315934291577314</v>
+        <v>0.5090028385608565</v>
       </c>
       <c r="D5">
-        <v>0.51071349060677496</v>
+        <v>0.5116238029874615</v>
       </c>
       <c r="E5">
-        <v>0.49953420265995091</v>
+        <v>0.5092698523736539</v>
       </c>
       <c r="F5">
-        <v>0.49196303339447661</v>
+        <v>0.5021830326224079</v>
       </c>
       <c r="G5">
-        <v>0.48794508736541731</v>
+        <v>0.4949943115781776</v>
       </c>
       <c r="H5">
-        <v>0.4740406172199958</v>
+        <v>0.4880837250570418</v>
       </c>
       <c r="I5">
-        <v>0.46444436302846931</v>
+        <v>0.4753683180382705</v>
       </c>
       <c r="J5">
-        <v>0.43900905760155862</v>
+        <v>0.4701777440021512</v>
       </c>
       <c r="K5">
-        <v>0.4293906815878325</v>
+        <v>0.4514872224966657</v>
       </c>
       <c r="L5">
-        <v>0.41283912220939301</v>
+        <v>0.4442541172535427</v>
       </c>
       <c r="M5">
-        <v>0.41164022939277822</v>
+        <v>0.4274478809280339</v>
       </c>
       <c r="N5">
-        <v>0.40434394069943341</v>
+        <v>0.4189807798555036</v>
       </c>
       <c r="O5">
-        <v>0.37891375765167712</v>
+        <v>0.4136378642138112</v>
       </c>
       <c r="P5">
-        <v>0.39605141387373849</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.3900086974913659</v>
+      </c>
+      <c r="Q5">
+        <v>0.4084101975347117</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>0.51161756540262537</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>0.51929472454801118</v>
+        <v>0.5106060331408332</v>
       </c>
       <c r="D6">
-        <v>0.52221614498941982</v>
+        <v>0.5166099987909847</v>
       </c>
       <c r="E6">
-        <v>0.50162755225359923</v>
+        <v>0.5177737991663687</v>
       </c>
       <c r="F6">
-        <v>0.51351350118965378</v>
+        <v>0.4932881889226371</v>
       </c>
       <c r="G6">
-        <v>0.47970396326487291</v>
+        <v>0.5081324862996012</v>
       </c>
       <c r="H6">
-        <v>0.48755045646446338</v>
+        <v>0.4674914847461178</v>
       </c>
       <c r="I6">
-        <v>0.46393805601232391</v>
+        <v>0.4719469239891128</v>
       </c>
       <c r="J6">
-        <v>0.46206382210455488</v>
+        <v>0.4516114121917285</v>
       </c>
       <c r="K6">
-        <v>0.450802608733609</v>
+        <v>0.4504755295862688</v>
       </c>
       <c r="L6">
-        <v>0.41524338283005258</v>
+        <v>0.4366089520054555</v>
       </c>
       <c r="M6">
-        <v>0.37984488654007448</v>
+        <v>0.4006708436375401</v>
       </c>
       <c r="N6">
-        <v>0.35064747062057061</v>
+        <v>0.3644334146492473</v>
       </c>
       <c r="O6">
-        <v>0.34600119735658191</v>
+        <v>0.3346188564769935</v>
       </c>
       <c r="P6">
-        <v>0.38366424298600899</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.3316350496380467</v>
+      </c>
+      <c r="Q6">
+        <v>0.3710515423580193</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>0.35549196811818651</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>0.50066486693535572</v>
+        <v>0.3562422916449842</v>
       </c>
       <c r="D7">
-        <v>0.5731317488647758</v>
+        <v>0.5019796372894144</v>
       </c>
       <c r="E7">
-        <v>0.61631159562716586</v>
+        <v>0.5751427714535972</v>
       </c>
       <c r="F7">
-        <v>0.63331021079577454</v>
+        <v>0.6186745278355046</v>
       </c>
       <c r="G7">
-        <v>0.64415500747855037</v>
+        <v>0.6368569443038044</v>
       </c>
       <c r="H7">
-        <v>0.62723397746655396</v>
+        <v>0.6467091977389301</v>
       </c>
       <c r="I7">
-        <v>0.6092394539952376</v>
+        <v>0.6304115774127418</v>
       </c>
       <c r="J7">
-        <v>0.59343257632877644</v>
+        <v>0.6131277330588342</v>
       </c>
       <c r="K7">
-        <v>0.5976480768881941</v>
+        <v>0.5978602488597108</v>
       </c>
       <c r="L7">
-        <v>0.53146892341862906</v>
+        <v>0.5980746031243421</v>
       </c>
       <c r="M7">
-        <v>0.54260230180341229</v>
+        <v>0.5356976984517863</v>
       </c>
       <c r="N7">
-        <v>0.5675090109304799</v>
+        <v>0.5442808665311296</v>
       </c>
       <c r="O7">
-        <v>0.56737803528327013</v>
+        <v>0.5728357986477352</v>
       </c>
       <c r="P7">
-        <v>0.56349351364868416</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.5715256816598416</v>
+      </c>
+      <c r="Q7">
+        <v>0.5667532497358443</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>0.41314942021117917</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>0.48167730349479598</v>
+        <v>0.4088159834092813</v>
       </c>
       <c r="D8">
-        <v>0.52107869760133263</v>
+        <v>0.4768570773488803</v>
       </c>
       <c r="E8">
-        <v>0.53766725694537898</v>
+        <v>0.5192187299814432</v>
       </c>
       <c r="F8">
-        <v>0.54355415796655004</v>
+        <v>0.5367449625591612</v>
       </c>
       <c r="G8">
-        <v>0.53560551694420633</v>
+        <v>0.5461890953645959</v>
       </c>
       <c r="H8">
-        <v>0.54398449656462844</v>
+        <v>0.5358775537882519</v>
       </c>
       <c r="I8">
-        <v>0.55660815950998255</v>
+        <v>0.544233768959312</v>
       </c>
       <c r="J8">
-        <v>0.49160259717392818</v>
+        <v>0.559074733237234</v>
       </c>
       <c r="K8">
-        <v>0.44851607846767028</v>
+        <v>0.4958788291436951</v>
       </c>
       <c r="L8">
-        <v>0.45230676321580882</v>
+        <v>0.458287751668938</v>
       </c>
       <c r="M8">
-        <v>0.4701911075680289</v>
+        <v>0.4643001697549228</v>
       </c>
       <c r="N8">
-        <v>0.49835785929857362</v>
+        <v>0.4806531680853978</v>
       </c>
       <c r="O8">
-        <v>0.47977541617484332</v>
+        <v>0.5101312681784608</v>
       </c>
       <c r="P8">
-        <v>0.48128587876427809</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.4896448253704312</v>
+      </c>
+      <c r="Q8">
+        <v>0.4919585997468403</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>0.41260322920368148</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>0.47900703448338727</v>
+        <v>0.4092041927732064</v>
       </c>
       <c r="D9">
-        <v>0.51868483101699792</v>
+        <v>0.4765222678485149</v>
       </c>
       <c r="E9">
-        <v>0.53312019719389137</v>
+        <v>0.517406126170302</v>
       </c>
       <c r="F9">
-        <v>0.54015477130058231</v>
+        <v>0.5326564681555604</v>
       </c>
       <c r="G9">
-        <v>0.53518913907105159</v>
+        <v>0.5390554694742238</v>
       </c>
       <c r="H9">
-        <v>0.54303921467699567</v>
+        <v>0.5314400322488948</v>
       </c>
       <c r="I9">
-        <v>0.55472267139643772</v>
+        <v>0.538743104233402</v>
       </c>
       <c r="J9">
-        <v>0.51092278500258781</v>
+        <v>0.5550345577645428</v>
       </c>
       <c r="K9">
-        <v>0.47485782141792993</v>
+        <v>0.5099189649276458</v>
       </c>
       <c r="L9">
-        <v>0.45428305356241527</v>
+        <v>0.4706304239143157</v>
       </c>
       <c r="M9">
-        <v>0.47228365591781968</v>
+        <v>0.4548010231475231</v>
       </c>
       <c r="N9">
-        <v>0.50940359575355276</v>
+        <v>0.4728652255172382</v>
       </c>
       <c r="O9">
-        <v>0.49742193145004288</v>
+        <v>0.5093904884545761</v>
       </c>
       <c r="P9">
-        <v>0.48710703750556011</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.4980329061954935</v>
+      </c>
+      <c r="Q9">
+        <v>0.488401632087914</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>0.41325271244798401</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>0.48182750537734548</v>
+        <v>0.4128225562787542</v>
       </c>
       <c r="D10">
-        <v>0.52620804420945311</v>
+        <v>0.4808649011701389</v>
       </c>
       <c r="E10">
-        <v>0.54231374484813311</v>
+        <v>0.5235252484876373</v>
       </c>
       <c r="F10">
-        <v>0.54677965501214709</v>
+        <v>0.5388440286724714</v>
       </c>
       <c r="G10">
-        <v>0.54108265591882265</v>
+        <v>0.5453667409768694</v>
       </c>
       <c r="H10">
-        <v>0.54875810744190301</v>
+        <v>0.5385269364892652</v>
       </c>
       <c r="I10">
-        <v>0.56439235864259885</v>
+        <v>0.5444961740795452</v>
       </c>
       <c r="J10">
-        <v>0.52305209103462924</v>
+        <v>0.5593337430217942</v>
       </c>
       <c r="K10">
-        <v>0.48935352180793812</v>
+        <v>0.5134128741894696</v>
       </c>
       <c r="L10">
-        <v>0.46433171367733572</v>
+        <v>0.4767515987184178</v>
       </c>
       <c r="M10">
-        <v>0.48166029474883931</v>
+        <v>0.4523848792093193</v>
       </c>
       <c r="N10">
-        <v>0.51736986667350338</v>
+        <v>0.4705041050811596</v>
       </c>
       <c r="O10">
-        <v>0.51165387665234319</v>
+        <v>0.5100405813190897</v>
       </c>
       <c r="P10">
-        <v>0.49673903778937101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.5044533928006266</v>
+      </c>
+      <c r="Q10">
+        <v>0.4930570880002664</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>0.41208113491732379</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>0.48063038175118239</v>
+        <v>0.4112781609996627</v>
       </c>
       <c r="D11">
-        <v>0.521870539692322</v>
+        <v>0.4790213468269075</v>
       </c>
       <c r="E11">
-        <v>0.53648880274073019</v>
+        <v>0.5188546797719036</v>
       </c>
       <c r="F11">
-        <v>0.53923704882810874</v>
+        <v>0.5354986251188254</v>
       </c>
       <c r="G11">
-        <v>0.53139569240491669</v>
+        <v>0.5397084650911829</v>
       </c>
       <c r="H11">
-        <v>0.53771585502094199</v>
+        <v>0.5345790229403099</v>
       </c>
       <c r="I11">
-        <v>0.55546076781556541</v>
+        <v>0.5436079751432232</v>
       </c>
       <c r="J11">
-        <v>0.51338913796927754</v>
+        <v>0.5579154525319442</v>
       </c>
       <c r="K11">
-        <v>0.47605769413716359</v>
+        <v>0.515395686578537</v>
       </c>
       <c r="L11">
-        <v>0.46207654210884558</v>
+        <v>0.475660312078532</v>
       </c>
       <c r="M11">
-        <v>0.47917871576351623</v>
+        <v>0.4580212256672241</v>
       </c>
       <c r="N11">
-        <v>0.50663338260690705</v>
+        <v>0.4724829215989539</v>
       </c>
       <c r="O11">
-        <v>0.486323826882052</v>
+        <v>0.4961161300727638</v>
       </c>
       <c r="P11">
-        <v>0.5065498521042523</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.4763678982415778</v>
+      </c>
+      <c r="Q11">
+        <v>0.5027299834880432</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>0.51729910153209291</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>0.52415700877901705</v>
+        <v>0.5178143320981872</v>
       </c>
       <c r="D12">
-        <v>0.52727268412032269</v>
+        <v>0.5268398320658604</v>
       </c>
       <c r="E12">
-        <v>0.52566381738400114</v>
+        <v>0.5318596076161383</v>
       </c>
       <c r="F12">
-        <v>0.53469652574865156</v>
+        <v>0.5324248526814376</v>
       </c>
       <c r="G12">
-        <v>0.53703418410459869</v>
+        <v>0.5395534379026514</v>
       </c>
       <c r="H12">
-        <v>0.53618296209151306</v>
+        <v>0.5357213561348312</v>
       </c>
       <c r="I12">
-        <v>0.52820572321641257</v>
+        <v>0.5323238528134414</v>
       </c>
       <c r="J12">
-        <v>0.51565486110253755</v>
+        <v>0.520581088799142</v>
       </c>
       <c r="K12">
-        <v>0.49880627971811659</v>
+        <v>0.5104947848381047</v>
       </c>
       <c r="L12">
-        <v>0.4736869045173514</v>
+        <v>0.4930137125485446</v>
       </c>
       <c r="M12">
-        <v>0.44640444270746188</v>
+        <v>0.4575855697914348</v>
       </c>
       <c r="N12">
-        <v>0.44268746067956771</v>
+        <v>0.4358903251894568</v>
       </c>
       <c r="O12">
-        <v>0.4194996516991682</v>
+        <v>0.4254066469186791</v>
       </c>
       <c r="P12">
-        <v>0.42226825103177568</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.4076074770262882</v>
+      </c>
+      <c r="Q12">
+        <v>0.4068875369878522</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>0.51680489875330338</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>0.53669345174357608</v>
+        <v>0.5198148372077717</v>
       </c>
       <c r="D13">
-        <v>0.54532994312533301</v>
+        <v>0.539355987351299</v>
       </c>
       <c r="E13">
-        <v>0.5486934942337518</v>
+        <v>0.5473270603557063</v>
       </c>
       <c r="F13">
-        <v>0.53918742424388466</v>
+        <v>0.5510762274700283</v>
       </c>
       <c r="G13">
-        <v>0.52773801694017741</v>
+        <v>0.5379640212410449</v>
       </c>
       <c r="H13">
-        <v>0.52307779528447473</v>
+        <v>0.5262190796108572</v>
       </c>
       <c r="I13">
-        <v>0.50283217350517651</v>
+        <v>0.5218090689302693</v>
       </c>
       <c r="J13">
-        <v>0.48955872549932788</v>
+        <v>0.4998234691956691</v>
       </c>
       <c r="K13">
-        <v>0.46357385235304788</v>
+        <v>0.4882815636312925</v>
       </c>
       <c r="L13">
-        <v>0.45293689265855658</v>
+        <v>0.4584822343000631</v>
       </c>
       <c r="M13">
-        <v>0.44520695838845392</v>
+        <v>0.4470919169171545</v>
       </c>
       <c r="N13">
-        <v>0.43184619855842071</v>
+        <v>0.4372909760076822</v>
       </c>
       <c r="O13">
-        <v>0.4155873245464845</v>
+        <v>0.4235155989834174</v>
       </c>
       <c r="P13">
-        <v>0.37907779107356632</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.4055605466349047</v>
+      </c>
+      <c r="Q13">
+        <v>0.3761579551206153</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>0.35869959951119917</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>0.50314235936684371</v>
+        <v>0.3556300908086379</v>
       </c>
       <c r="D14">
-        <v>0.57618662798384113</v>
+        <v>0.5026523760031051</v>
       </c>
       <c r="E14">
-        <v>0.62004074434758627</v>
+        <v>0.5745105946564838</v>
       </c>
       <c r="F14">
-        <v>0.63827515769940513</v>
+        <v>0.6162204533741243</v>
       </c>
       <c r="G14">
-        <v>0.64390748862054004</v>
+        <v>0.6335571054094424</v>
       </c>
       <c r="H14">
-        <v>0.63327654576991865</v>
+        <v>0.6407468425140717</v>
       </c>
       <c r="I14">
-        <v>0.61547241078221504</v>
+        <v>0.6274985262830733</v>
       </c>
       <c r="J14">
-        <v>0.59752913917954176</v>
+        <v>0.611472838250809</v>
       </c>
       <c r="K14">
-        <v>0.59193551640593556</v>
+        <v>0.5945122382259547</v>
       </c>
       <c r="L14">
-        <v>0.51891153207600149</v>
+        <v>0.5922816691758386</v>
       </c>
       <c r="M14">
-        <v>0.51417326933619378</v>
+        <v>0.5165821304034495</v>
       </c>
       <c r="N14">
-        <v>0.53902994027421725</v>
+        <v>0.5108700715656681</v>
       </c>
       <c r="O14">
-        <v>0.55182435903316507</v>
+        <v>0.5385610210760607</v>
       </c>
       <c r="P14">
-        <v>0.56720079470902462</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.5460040322609367</v>
+      </c>
+      <c r="Q14">
+        <v>0.5607181865183933</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>0.35442647896270141</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>0.49889225550075372</v>
+        <v>0.3569715394935229</v>
       </c>
       <c r="D15">
-        <v>0.57328960482521552</v>
+        <v>0.5029880644157873</v>
       </c>
       <c r="E15">
-        <v>0.6161644892993795</v>
+        <v>0.5759436262842809</v>
       </c>
       <c r="F15">
-        <v>0.63396181713156852</v>
+        <v>0.6178527627783974</v>
       </c>
       <c r="G15">
-        <v>0.64149892936945685</v>
+        <v>0.6351796954631146</v>
       </c>
       <c r="H15">
-        <v>0.62616790667252498</v>
+        <v>0.6436052782488723</v>
       </c>
       <c r="I15">
-        <v>0.61069865037460835</v>
+        <v>0.6292816972452426</v>
       </c>
       <c r="J15">
-        <v>0.59736349329601779</v>
+        <v>0.615038138268479</v>
       </c>
       <c r="K15">
-        <v>0.59229621778649932</v>
+        <v>0.5992453699179219</v>
       </c>
       <c r="L15">
-        <v>0.52462942729449291</v>
+        <v>0.596634230660974</v>
       </c>
       <c r="M15">
-        <v>0.51105960129114125</v>
+        <v>0.5293928257424672</v>
       </c>
       <c r="N15">
-        <v>0.53367287297373833</v>
+        <v>0.5148820657284644</v>
       </c>
       <c r="O15">
-        <v>0.54370123970766682</v>
+        <v>0.5353636153350304</v>
       </c>
       <c r="P15">
-        <v>0.56088212026636586</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.5474302846020803</v>
+      </c>
+      <c r="Q15">
+        <v>0.5641502306645447</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>0.36017689441097372</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>0.50481121432938336</v>
+        <v>0.3563229561833459</v>
       </c>
       <c r="D16">
-        <v>0.57660016052233454</v>
+        <v>0.5029603138682869</v>
       </c>
       <c r="E16">
-        <v>0.61787842464422249</v>
+        <v>0.5764499919222311</v>
       </c>
       <c r="F16">
-        <v>0.63672143237439371</v>
+        <v>0.6190357929965044</v>
       </c>
       <c r="G16">
-        <v>0.64588986526667591</v>
+        <v>0.6370151002013615</v>
       </c>
       <c r="H16">
-        <v>0.6310117050660583</v>
+        <v>0.645235599281476</v>
       </c>
       <c r="I16">
-        <v>0.6182443481816301</v>
+        <v>0.6306985327224948</v>
       </c>
       <c r="J16">
-        <v>0.60382098669524675</v>
+        <v>0.6167845894753862</v>
       </c>
       <c r="K16">
-        <v>0.60015344607679955</v>
+        <v>0.6007713974658112</v>
       </c>
       <c r="L16">
-        <v>0.53424687594308595</v>
+        <v>0.5995366450468019</v>
       </c>
       <c r="M16">
-        <v>0.52442770762340052</v>
+        <v>0.5335382568270355</v>
       </c>
       <c r="N16">
-        <v>0.54731509186102012</v>
+        <v>0.5218602639337184</v>
       </c>
       <c r="O16">
-        <v>0.55457395604829696</v>
+        <v>0.5441951979573075</v>
       </c>
       <c r="P16">
-        <v>0.5698701170992817</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.5488668519304026</v>
+      </c>
+      <c r="Q16">
+        <v>0.5633071020967771</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>0.3571896038377142</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>0.50171261455023908</v>
+        <v>0.3560309003300657</v>
       </c>
       <c r="D17">
-        <v>0.57667027717426156</v>
+        <v>0.5010511429299664</v>
       </c>
       <c r="E17">
-        <v>0.61894593821427801</v>
+        <v>0.5708273807599105</v>
       </c>
       <c r="F17">
-        <v>0.63649525970291432</v>
+        <v>0.6142385511786806</v>
       </c>
       <c r="G17">
-        <v>0.64524631837489432</v>
+        <v>0.6328357413252318</v>
       </c>
       <c r="H17">
-        <v>0.63260501262731283</v>
+        <v>0.6411876835225249</v>
       </c>
       <c r="I17">
-        <v>0.62014516098486927</v>
+        <v>0.6286261741899991</v>
       </c>
       <c r="J17">
-        <v>0.60464731803167693</v>
+        <v>0.6119497462383318</v>
       </c>
       <c r="K17">
-        <v>0.60268752776100831</v>
+        <v>0.5968690610227958</v>
       </c>
       <c r="L17">
-        <v>0.53991933753520405</v>
+        <v>0.5961919008425232</v>
       </c>
       <c r="M17">
-        <v>0.52983388569782364</v>
+        <v>0.5290878669253014</v>
       </c>
       <c r="N17">
-        <v>0.55553053606916614</v>
+        <v>0.5242590811596626</v>
       </c>
       <c r="O17">
-        <v>0.56467676088886565</v>
+        <v>0.548946701134816</v>
       </c>
       <c r="P17">
-        <v>0.57965464274420764</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.5571797567168639</v>
+      </c>
+      <c r="Q17">
+        <v>0.574389074072236</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>0.51797864607635247</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>0.52386311910304018</v>
+        <v>0.5217863216895706</v>
       </c>
       <c r="D18">
-        <v>0.52123277150530156</v>
+        <v>0.5263910347594016</v>
       </c>
       <c r="E18">
-        <v>0.5209988266489799</v>
+        <v>0.526211864714922</v>
       </c>
       <c r="F18">
-        <v>0.54233280752728052</v>
+        <v>0.5238433318152028</v>
       </c>
       <c r="G18">
-        <v>0.52747156769285641</v>
+        <v>0.5417236009608192</v>
       </c>
       <c r="H18">
-        <v>0.53574013434755863</v>
+        <v>0.5275470504261861</v>
       </c>
       <c r="I18">
-        <v>0.53706263232190377</v>
+        <v>0.5415585920530469</v>
       </c>
       <c r="J18">
-        <v>0.53780906218453894</v>
+        <v>0.5382239235317829</v>
       </c>
       <c r="K18">
-        <v>0.53879414671012771</v>
+        <v>0.5391760121695129</v>
       </c>
       <c r="L18">
-        <v>0.54034079305098948</v>
+        <v>0.5391479485043063</v>
       </c>
       <c r="M18">
-        <v>0.52831381882334616</v>
+        <v>0.5395706272974928</v>
       </c>
       <c r="N18">
-        <v>0.52532290999306563</v>
+        <v>0.5292126218108919</v>
       </c>
       <c r="O18">
-        <v>0.5050732876023164</v>
+        <v>0.5274454100816942</v>
       </c>
       <c r="P18">
-        <v>0.51510697498485503</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.5099330653548149</v>
+      </c>
+      <c r="Q18">
+        <v>0.5200679452465269</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>0.52203899715557101</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.53259622556518105</v>
+        <v>0.5239535390222806</v>
       </c>
       <c r="D19">
-        <v>0.53859304909455052</v>
+        <v>0.5339707017758634</v>
       </c>
       <c r="E19">
-        <v>0.52443502891551241</v>
+        <v>0.5407619164503057</v>
       </c>
       <c r="F19">
-        <v>0.54130634918875364</v>
+        <v>0.5268953789532813</v>
       </c>
       <c r="G19">
-        <v>0.53497720455812348</v>
+        <v>0.5453062558760206</v>
       </c>
       <c r="H19">
-        <v>0.54513031898998598</v>
+        <v>0.5389924016680434</v>
       </c>
       <c r="I19">
-        <v>0.53902049172659428</v>
+        <v>0.5510287729327278</v>
       </c>
       <c r="J19">
-        <v>0.53987984630845054</v>
+        <v>0.5411265763970804</v>
       </c>
       <c r="K19">
-        <v>0.55371879348298003</v>
+        <v>0.5426596770204405</v>
       </c>
       <c r="L19">
-        <v>0.52803323903077437</v>
+        <v>0.5563041032571227</v>
       </c>
       <c r="M19">
-        <v>0.51381054771521961</v>
+        <v>0.5310655586712237</v>
       </c>
       <c r="N19">
-        <v>0.5107716838981432</v>
+        <v>0.5124568463762758</v>
       </c>
       <c r="O19">
-        <v>0.50393672550320956</v>
+        <v>0.5148760996559234</v>
       </c>
       <c r="P19">
-        <v>0.51513828881996937</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.5062402207780643</v>
+      </c>
+      <c r="Q19">
+        <v>0.5186978190881314</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>0.5225277358788446</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>0.53493320106181108</v>
+        <v>0.5212221986825375</v>
       </c>
       <c r="D20">
-        <v>0.55016631578332342</v>
+        <v>0.5313610778042328</v>
       </c>
       <c r="E20">
-        <v>0.52605565946482247</v>
+        <v>0.5422755282963931</v>
       </c>
       <c r="F20">
-        <v>0.52621475676318796</v>
+        <v>0.5215535428590623</v>
       </c>
       <c r="G20">
-        <v>0.54353396930093412</v>
+        <v>0.5221797844874695</v>
       </c>
       <c r="H20">
-        <v>0.56896812314820444</v>
+        <v>0.5404627765811006</v>
       </c>
       <c r="I20">
-        <v>0.54909775222047674</v>
+        <v>0.5593400461782969</v>
       </c>
       <c r="J20">
-        <v>0.55658150736013512</v>
+        <v>0.54100123672976</v>
       </c>
       <c r="K20">
-        <v>0.55522931297586853</v>
+        <v>0.5482409758981931</v>
       </c>
       <c r="L20">
-        <v>0.54069917936182754</v>
+        <v>0.5468940382329971</v>
       </c>
       <c r="M20">
-        <v>0.51699753845212704</v>
+        <v>0.5300599938326559</v>
       </c>
       <c r="N20">
-        <v>0.51417587883998361</v>
+        <v>0.5084977166109405</v>
       </c>
       <c r="O20">
-        <v>0.54261083014400546</v>
+        <v>0.5019947562408947</v>
       </c>
       <c r="P20">
-        <v>0.54256126142993943</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.5315443330232297</v>
+      </c>
+      <c r="Q20">
+        <v>0.531764299309848</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>0.42057709490614797</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>0.51670098699458011</v>
+        <v>0.417064440857057</v>
       </c>
       <c r="D21">
-        <v>0.52670537964542485</v>
+        <v>0.516651521169609</v>
       </c>
       <c r="E21">
-        <v>0.54020088382550813</v>
+        <v>0.527369613690158</v>
       </c>
       <c r="F21">
-        <v>0.53193775329528903</v>
+        <v>0.5443626112546683</v>
       </c>
       <c r="G21">
-        <v>0.52260856909014364</v>
+        <v>0.5311236463348813</v>
       </c>
       <c r="H21">
-        <v>0.46099523724767749</v>
+        <v>0.521761351564781</v>
       </c>
       <c r="I21">
-        <v>0.44425323456914811</v>
+        <v>0.4626566008977575</v>
       </c>
       <c r="J21">
-        <v>0.4376444977574877</v>
+        <v>0.445346917200093</v>
       </c>
       <c r="K21">
-        <v>0.415752173742516</v>
+        <v>0.4402704908425608</v>
       </c>
       <c r="L21">
-        <v>0.3808380262744897</v>
+        <v>0.4148556085215171</v>
       </c>
       <c r="M21">
-        <v>0.3452501080304623</v>
+        <v>0.3767155340436225</v>
       </c>
       <c r="N21">
-        <v>0.29736638558231149</v>
+        <v>0.340406270661112</v>
       </c>
       <c r="O21">
-        <v>0.2317809479946496</v>
+        <v>0.2929342318742477</v>
       </c>
       <c r="P21">
-        <v>0.16228976580741161</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.2284097985257858</v>
+      </c>
+      <c r="Q21">
+        <v>0.1581303611617724</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>0.41875423864881539</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>0.5162608916060436</v>
+        <v>0.4170224777797645</v>
       </c>
       <c r="D22">
-        <v>0.5249619196751677</v>
+        <v>0.5144370549090203</v>
       </c>
       <c r="E22">
-        <v>0.53471061786487173</v>
+        <v>0.5226833111750913</v>
       </c>
       <c r="F22">
-        <v>0.52637198764000293</v>
+        <v>0.536413973760368</v>
       </c>
       <c r="G22">
-        <v>0.52901684892551459</v>
+        <v>0.5291761574952422</v>
       </c>
       <c r="H22">
-        <v>0.46101959360772438</v>
+        <v>0.532075599123266</v>
       </c>
       <c r="I22">
-        <v>0.43184112283558052</v>
+        <v>0.4646239618413164</v>
       </c>
       <c r="J22">
-        <v>0.42911575555027082</v>
+        <v>0.4393632183838218</v>
       </c>
       <c r="K22">
-        <v>0.41292871838913758</v>
+        <v>0.4393347579627212</v>
       </c>
       <c r="L22">
-        <v>0.37506981531875327</v>
+        <v>0.424025415608824</v>
       </c>
       <c r="M22">
-        <v>0.33921220800694352</v>
+        <v>0.3834244360623873</v>
       </c>
       <c r="N22">
-        <v>0.29492150341147799</v>
+        <v>0.3447475709850321</v>
       </c>
       <c r="O22">
-        <v>0.2274300287745189</v>
+        <v>0.3003298360816458</v>
       </c>
       <c r="P22">
-        <v>0.17045172081754331</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.2289096399388858</v>
+      </c>
+      <c r="Q22">
+        <v>0.1784689209121892</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>0.51505765195566022</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>0.47886634144836487</v>
+        <v>0.5196261515635653</v>
       </c>
       <c r="D23">
-        <v>0.51019179835413897</v>
+        <v>0.4902202171881263</v>
       </c>
       <c r="E23">
-        <v>0.52683194232927899</v>
+        <v>0.5203090939604649</v>
       </c>
       <c r="F23">
-        <v>0.48409841153792771</v>
+        <v>0.5306185399747748</v>
       </c>
       <c r="G23">
-        <v>0.43448589533513238</v>
+        <v>0.4949091731905486</v>
       </c>
       <c r="H23">
-        <v>0.36267851399087231</v>
+        <v>0.4472178373407638</v>
       </c>
       <c r="I23">
-        <v>0.35102325823823077</v>
+        <v>0.3696121360639208</v>
       </c>
       <c r="J23">
-        <v>0.30166349291404149</v>
+        <v>0.3558942332944692</v>
       </c>
       <c r="K23">
-        <v>0.26669643373730889</v>
+        <v>0.3103841128687425</v>
       </c>
       <c r="L23">
-        <v>0.22328236370976309</v>
+        <v>0.280411358351219</v>
       </c>
       <c r="M23">
-        <v>0.20519943985969299</v>
+        <v>0.2423432457273525</v>
       </c>
       <c r="N23">
-        <v>0.15566501895974319</v>
+        <v>0.220990136074922</v>
       </c>
       <c r="O23">
-        <v>0.10713528250855441</v>
+        <v>0.1767771818408736</v>
       </c>
       <c r="P23">
-        <v>4.7219323811258179E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.1265082298489208</v>
+      </c>
+      <c r="Q23">
+        <v>0.06670911437065258</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>7.9644270843617831E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>1.0457558088178239E-2</v>
+        <v>0.5375244686628426</v>
       </c>
       <c r="D24">
-        <v>2.983693508975541E-2</v>
+        <v>0.6035531210656815</v>
       </c>
       <c r="E24">
-        <v>-8.402635933129092E-2</v>
+        <v>0.6414660330443179</v>
       </c>
       <c r="F24">
-        <v>-0.36944332593524548</v>
+        <v>0.665132618855938</v>
       </c>
       <c r="G24">
-        <v>-0.25591932650439952</v>
+        <v>0.6382689272467466</v>
       </c>
       <c r="H24">
-        <v>-0.32304446917578711</v>
+        <v>0.6222603645373472</v>
       </c>
       <c r="I24">
-        <v>-0.37949463010762691</v>
+        <v>0.625861103593613</v>
       </c>
       <c r="J24">
-        <v>-0.42402360897274638</v>
+        <v>0.6034405893202937</v>
       </c>
       <c r="K24">
-        <v>-0.48780252787470751</v>
+        <v>0.6394627188055857</v>
       </c>
       <c r="L24">
-        <v>-0.54808675460587764</v>
+        <v>0.6547497971736996</v>
       </c>
       <c r="M24">
-        <v>-0.55072484803656596</v>
+        <v>0.6190193177598117</v>
       </c>
       <c r="N24">
-        <v>-0.53904803974386428</v>
+        <v>0.6018891193248577</v>
       </c>
       <c r="O24">
-        <v>-0.57144008787599532</v>
+        <v>0.5667156965346349</v>
       </c>
       <c r="P24">
-        <v>-0.59059135381604821</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>0.5409282856910196</v>
+      </c>
+      <c r="Q24">
+        <v>0.4966937920059543</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>5.8540258842796518E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>8.6863039193726208E-3</v>
+        <v>0.5383364304728476</v>
       </c>
       <c r="D25">
-        <v>-3.573713536710358E-2</v>
+        <v>0.6095401669543319</v>
       </c>
       <c r="E25">
-        <v>-0.13505477135410671</v>
+        <v>0.6572227515464977</v>
       </c>
       <c r="F25">
-        <v>-0.2165552082413672</v>
+        <v>0.6889913600008079</v>
       </c>
       <c r="G25">
-        <v>-0.36716566553368091</v>
+        <v>0.6816671976364757</v>
       </c>
       <c r="H25">
-        <v>-0.48150694953216688</v>
+        <v>0.6950456061730974</v>
       </c>
       <c r="I25">
-        <v>-0.5654212439002545</v>
+        <v>0.6880072711600674</v>
       </c>
       <c r="J25">
-        <v>-0.57714772591060237</v>
+        <v>0.6786818916299407</v>
       </c>
       <c r="K25">
-        <v>-0.57067366728546787</v>
+        <v>0.7144324750775378</v>
       </c>
       <c r="L25">
-        <v>-0.66586555932537128</v>
+        <v>0.7185444951420671</v>
       </c>
       <c r="M25">
-        <v>-0.76437479493410587</v>
+        <v>0.7161677543520855</v>
       </c>
       <c r="N25">
-        <v>-0.84996996481406828</v>
+        <v>0.7048912478981381</v>
       </c>
       <c r="O25">
-        <v>-0.86416685212238076</v>
+        <v>0.6848979859663268</v>
       </c>
       <c r="P25">
-        <v>-0.88009174105524068</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>0.6650498784543839</v>
+      </c>
+      <c r="Q25">
+        <v>0.6312380067316581</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>7.108703845491024E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>3.8460448793727148E-2</v>
+        <v>0.5535758519039772</v>
       </c>
       <c r="D26">
-        <v>2.9359571346470919E-2</v>
+        <v>0.5893361778861764</v>
       </c>
       <c r="E26">
-        <v>-6.529398830007685E-2</v>
+        <v>0.6311234684378755</v>
       </c>
       <c r="F26">
-        <v>-0.15351093809088179</v>
+        <v>0.6574459922444396</v>
       </c>
       <c r="G26">
-        <v>-0.17683522653200789</v>
+        <v>0.6377013749380548</v>
       </c>
       <c r="H26">
-        <v>-0.23923241628540889</v>
+        <v>0.659217075670378</v>
       </c>
       <c r="I26">
-        <v>-0.20442471186157379</v>
+        <v>0.6471879813340597</v>
       </c>
       <c r="J26">
-        <v>-0.1508328446926665</v>
+        <v>0.6450397311284045</v>
       </c>
       <c r="K26">
-        <v>-0.1001837964242487</v>
+        <v>0.6484386974201108</v>
       </c>
       <c r="L26">
-        <v>-0.25983736372444011</v>
+        <v>0.6683962441406193</v>
       </c>
       <c r="M26">
-        <v>-0.42946163823866651</v>
+        <v>0.6594203382855369</v>
       </c>
       <c r="N26">
-        <v>-0.37654590076280642</v>
+        <v>0.6568794136162467</v>
       </c>
       <c r="O26">
-        <v>-0.41109419022900501</v>
+        <v>0.6350595508932341</v>
       </c>
       <c r="P26">
-        <v>-0.43094556808729451</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.6025823571904891</v>
+      </c>
+      <c r="Q26">
+        <v>0.5670950131642235</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>5.2031678223643733E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>2.682422418858911E-2</v>
+        <v>0.5532820878955533</v>
       </c>
       <c r="D27">
-        <v>-9.2785178565100879E-2</v>
+        <v>0.5879663656710206</v>
       </c>
       <c r="E27">
-        <v>-4.9464444755769353E-2</v>
+        <v>0.6303254216237832</v>
       </c>
       <c r="F27">
-        <v>-0.15967070243238571</v>
+        <v>0.6569368859572371</v>
       </c>
       <c r="G27">
-        <v>-0.1412756359368397</v>
+        <v>0.6406015746725331</v>
       </c>
       <c r="H27">
-        <v>-6.7576830622424713E-2</v>
+        <v>0.6514165560601104</v>
       </c>
       <c r="I27">
-        <v>-6.1966982595869982E-2</v>
+        <v>0.6452720780286789</v>
       </c>
       <c r="J27">
-        <v>-0.13841242502987469</v>
+        <v>0.638375151974253</v>
       </c>
       <c r="K27">
-        <v>-0.22600311736729159</v>
+        <v>0.6320989766799943</v>
       </c>
       <c r="L27">
-        <v>-0.29171910319469901</v>
+        <v>0.6396479371717138</v>
       </c>
       <c r="M27">
-        <v>-0.35214812360481879</v>
+        <v>0.6348939075919481</v>
       </c>
       <c r="N27">
-        <v>-0.28041367642717829</v>
+        <v>0.6378074188777868</v>
       </c>
       <c r="O27">
-        <v>-0.37822942852032748</v>
+        <v>0.6287716298354772</v>
       </c>
       <c r="P27">
-        <v>-0.41731626433628061</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.6123649606803856</v>
+      </c>
+      <c r="Q27">
+        <v>0.61920748239145</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>0.53764249568630307</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>0.60300762523922768</v>
+        <v>0.5363873730823653</v>
       </c>
       <c r="D28">
-        <v>0.63810567966071008</v>
+        <v>0.6038798149014128</v>
       </c>
       <c r="E28">
-        <v>0.66337350103404746</v>
+        <v>0.6485160654332489</v>
       </c>
       <c r="F28">
-        <v>0.63405121020682365</v>
+        <v>0.6817288441802017</v>
       </c>
       <c r="G28">
-        <v>0.6222558463123733</v>
+        <v>0.6692268504931994</v>
       </c>
       <c r="H28">
-        <v>0.61907802399061274</v>
+        <v>0.6816331863434703</v>
       </c>
       <c r="I28">
-        <v>0.60388045054354567</v>
+        <v>0.6712267220156927</v>
       </c>
       <c r="J28">
-        <v>0.63867556542704851</v>
+        <v>0.6469970433518409</v>
       </c>
       <c r="K28">
-        <v>0.65823530441312239</v>
+        <v>0.681279017618773</v>
       </c>
       <c r="L28">
-        <v>0.6237605134669717</v>
+        <v>0.6869861992380368</v>
       </c>
       <c r="M28">
-        <v>0.60357910833741046</v>
+        <v>0.695786379564286</v>
       </c>
       <c r="N28">
-        <v>0.57154647203711773</v>
+        <v>0.6897978437784966</v>
       </c>
       <c r="O28">
-        <v>0.55029852239743349</v>
+        <v>0.6753645203736266</v>
       </c>
       <c r="P28">
-        <v>0.50844667484834372</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.6646037699315356</v>
+      </c>
+      <c r="Q28">
+        <v>0.6322220429280399</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>0.53640501969873267</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>0.60449557833617318</v>
+        <v>0.537307957786249</v>
       </c>
       <c r="D29">
-        <v>0.65165626243910213</v>
+        <v>0.6056969204922473</v>
       </c>
       <c r="E29">
-        <v>0.68469643711004613</v>
+        <v>0.6529335140752119</v>
       </c>
       <c r="F29">
-        <v>0.6774606094355865</v>
+        <v>0.6875985478271688</v>
       </c>
       <c r="G29">
-        <v>0.69000245891586509</v>
+        <v>0.6806889944047018</v>
       </c>
       <c r="H29">
-        <v>0.68400800667691164</v>
+        <v>0.689984016811363</v>
       </c>
       <c r="I29">
-        <v>0.67428261608935181</v>
+        <v>0.6872529375438008</v>
       </c>
       <c r="J29">
-        <v>0.71151874273345783</v>
+        <v>0.6665833473052942</v>
       </c>
       <c r="K29">
-        <v>0.71001028536625155</v>
+        <v>0.6941131930715417</v>
       </c>
       <c r="L29">
-        <v>0.71073235553634562</v>
+        <v>0.6984272278984444</v>
       </c>
       <c r="M29">
-        <v>0.69685545988120523</v>
+        <v>0.7067254387199235</v>
       </c>
       <c r="N29">
-        <v>0.6797901466876739</v>
+        <v>0.6989006263208087</v>
       </c>
       <c r="O29">
-        <v>0.65552569570001762</v>
+        <v>0.6836790626959056</v>
       </c>
       <c r="P29">
-        <v>0.62176336988606318</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.6697021720916623</v>
+      </c>
+      <c r="Q29">
+        <v>0.6281714534704657</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>0.55261419036347614</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>0.58729817697553022</v>
+        <v>0.5364613844423952</v>
       </c>
       <c r="D30">
-        <v>0.62649135357069707</v>
+        <v>0.605744099486981</v>
       </c>
       <c r="E30">
-        <v>0.65325144659820766</v>
+        <v>0.6518977403425845</v>
       </c>
       <c r="F30">
-        <v>0.63513690082954777</v>
+        <v>0.6841152419190871</v>
       </c>
       <c r="G30">
-        <v>0.65428835054863688</v>
+        <v>0.6758876064671968</v>
       </c>
       <c r="H30">
-        <v>0.64358591556897626</v>
+        <v>0.6841058476429653</v>
       </c>
       <c r="I30">
-        <v>0.63716105489957975</v>
+        <v>0.6777630396035154</v>
       </c>
       <c r="J30">
-        <v>0.64325299926513435</v>
+        <v>0.6522652406826274</v>
       </c>
       <c r="K30">
-        <v>0.66384424717051482</v>
+        <v>0.6857349461072995</v>
       </c>
       <c r="L30">
-        <v>0.65420399928641026</v>
+        <v>0.6894176451662697</v>
       </c>
       <c r="M30">
-        <v>0.65120673138108709</v>
+        <v>0.7014810104026123</v>
       </c>
       <c r="N30">
-        <v>0.62675121614276796</v>
+        <v>0.695583339678591</v>
       </c>
       <c r="O30">
-        <v>0.59329339582405605</v>
+        <v>0.6798378661253881</v>
       </c>
       <c r="P30">
-        <v>0.55497656606051893</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.6656196718188155</v>
+      </c>
+      <c r="Q30">
+        <v>0.6230133288914946</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>0.55395937000236062</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>0.58966516266318203</v>
+        <v>0.5366785959995182</v>
       </c>
       <c r="D31">
-        <v>0.63031215435078125</v>
+        <v>0.6063459013986519</v>
       </c>
       <c r="E31">
-        <v>0.65498780850518701</v>
+        <v>0.6508729718868922</v>
       </c>
       <c r="F31">
-        <v>0.63713754866504135</v>
+        <v>0.6847808890945443</v>
       </c>
       <c r="G31">
-        <v>0.65428100772031728</v>
+        <v>0.6769378251184748</v>
       </c>
       <c r="H31">
-        <v>0.64564531390126456</v>
+        <v>0.6862138101734214</v>
       </c>
       <c r="I31">
-        <v>0.63893349804073074</v>
+        <v>0.6810149866122462</v>
       </c>
       <c r="J31">
-        <v>0.63129883772732809</v>
+        <v>0.6568410275512718</v>
       </c>
       <c r="K31">
-        <v>0.63598297324612352</v>
+        <v>0.6884527503185418</v>
       </c>
       <c r="L31">
-        <v>0.6335405713586465</v>
+        <v>0.6917478581837183</v>
       </c>
       <c r="M31">
-        <v>0.63673720254380262</v>
+        <v>0.7031405737371821</v>
       </c>
       <c r="N31">
-        <v>0.62825234098003357</v>
+        <v>0.6957446337267023</v>
       </c>
       <c r="O31">
-        <v>0.60685576226673477</v>
+        <v>0.6800726335755358</v>
       </c>
       <c r="P31">
-        <v>0.61576750057649943</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.6729657150401801</v>
+      </c>
+      <c r="Q31">
+        <v>0.6358014555826821</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>0.53715974804411426</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>0.60532508889636683</v>
+        <v>0.5378992518361592</v>
       </c>
       <c r="D32">
-        <v>0.65039773168920356</v>
+        <v>0.6053383637806783</v>
       </c>
       <c r="E32">
-        <v>0.68398026907034282</v>
+        <v>0.6507892449016813</v>
       </c>
       <c r="F32">
-        <v>0.67299186974523817</v>
+        <v>0.683658348344143</v>
       </c>
       <c r="G32">
-        <v>0.682992630704506</v>
+        <v>0.672059874611121</v>
       </c>
       <c r="H32">
-        <v>0.67817102287333531</v>
+        <v>0.683938621051172</v>
       </c>
       <c r="I32">
-        <v>0.65344240839786483</v>
+        <v>0.675277189439341</v>
       </c>
       <c r="J32">
-        <v>0.6826207362636274</v>
+        <v>0.6545377850749061</v>
       </c>
       <c r="K32">
-        <v>0.68736955406188727</v>
+        <v>0.683891244650472</v>
       </c>
       <c r="L32">
-        <v>0.69517679590895631</v>
+        <v>0.6859914062614304</v>
       </c>
       <c r="M32">
-        <v>0.6896447982648134</v>
+        <v>0.6901081027452974</v>
       </c>
       <c r="N32">
-        <v>0.6737536369169187</v>
+        <v>0.6835019654821517</v>
       </c>
       <c r="O32">
-        <v>0.66249627896120711</v>
+        <v>0.6692621174013174</v>
       </c>
       <c r="P32">
-        <v>0.62520012693425753</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.6624604806095933</v>
+      </c>
+      <c r="Q32">
+        <v>0.6259977210674469</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>0.53763870974136874</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>0.60583665350687066</v>
+        <v>0.5376802751238955</v>
       </c>
       <c r="D33">
-        <v>0.65192067640341778</v>
+        <v>0.605346774336592</v>
       </c>
       <c r="E33">
-        <v>0.68458883975270401</v>
+        <v>0.6505711518929833</v>
       </c>
       <c r="F33">
-        <v>0.67482936777830838</v>
+        <v>0.6841315430392105</v>
       </c>
       <c r="G33">
-        <v>0.68374799252797336</v>
+        <v>0.6750240867986625</v>
       </c>
       <c r="H33">
-        <v>0.67885347106138516</v>
+        <v>0.6848867060797919</v>
       </c>
       <c r="I33">
-        <v>0.65497964859637026</v>
+        <v>0.6774263645605254</v>
       </c>
       <c r="J33">
-        <v>0.69070443262393622</v>
+        <v>0.6577124599426059</v>
       </c>
       <c r="K33">
-        <v>0.69118212479926899</v>
+        <v>0.6863630802834656</v>
       </c>
       <c r="L33">
-        <v>0.70126385664153856</v>
+        <v>0.6845882877419369</v>
       </c>
       <c r="M33">
-        <v>0.69296958320835611</v>
+        <v>0.6933501956330749</v>
       </c>
       <c r="N33">
-        <v>0.67787979303906698</v>
+        <v>0.6839336150570692</v>
       </c>
       <c r="O33">
-        <v>0.66173613501862338</v>
+        <v>0.6708913511103077</v>
       </c>
       <c r="P33">
-        <v>0.62360953332997704</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.6574462970279188</v>
+      </c>
+      <c r="Q33">
+        <v>0.6189144329043661</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>0.5371701134534127</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>0.60553124781495105</v>
+        <v>0.535963145122751</v>
       </c>
       <c r="D34">
-        <v>0.65142564582459817</v>
+        <v>0.6049491915200378</v>
       </c>
       <c r="E34">
-        <v>0.68433494367609538</v>
+        <v>0.6508652848983104</v>
       </c>
       <c r="F34">
-        <v>0.67450668657063073</v>
+        <v>0.6847701624460306</v>
       </c>
       <c r="G34">
-        <v>0.68659565320418958</v>
+        <v>0.6758156346232044</v>
       </c>
       <c r="H34">
-        <v>0.68032026294405656</v>
+        <v>0.6860297286388227</v>
       </c>
       <c r="I34">
-        <v>0.6564205059461774</v>
+        <v>0.6803939701013758</v>
       </c>
       <c r="J34">
-        <v>0.68626163282254404</v>
+        <v>0.6623285999642538</v>
       </c>
       <c r="K34">
-        <v>0.69408613475919156</v>
+        <v>0.6891628179741449</v>
       </c>
       <c r="L34">
-        <v>0.7045663376125868</v>
+        <v>0.6888434845176415</v>
       </c>
       <c r="M34">
-        <v>0.69701526781314693</v>
+        <v>0.6955392014615173</v>
       </c>
       <c r="N34">
-        <v>0.67911056560695249</v>
+        <v>0.6914513522962592</v>
       </c>
       <c r="O34">
-        <v>0.66860881045819798</v>
+        <v>0.6765827570811745</v>
       </c>
       <c r="P34">
-        <v>0.62807741521494032</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.6667344618088162</v>
+      </c>
+      <c r="Q34">
+        <v>0.6248626098774351</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>0.5371442764375467</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>0.60558759206344648</v>
+        <v>0.5370659416555084</v>
       </c>
       <c r="D35">
-        <v>0.65040884292295331</v>
+        <v>0.6059714994557528</v>
       </c>
       <c r="E35">
-        <v>0.68471137442880259</v>
+        <v>0.6520030860302849</v>
       </c>
       <c r="F35">
-        <v>0.67637843174079881</v>
+        <v>0.6844834710453001</v>
       </c>
       <c r="G35">
-        <v>0.68645692274414327</v>
+        <v>0.6754672307690751</v>
       </c>
       <c r="H35">
-        <v>0.68036347732204416</v>
+        <v>0.6866759717311915</v>
       </c>
       <c r="I35">
-        <v>0.65602116476057204</v>
+        <v>0.6812735392110196</v>
       </c>
       <c r="J35">
-        <v>0.68869106243119038</v>
+        <v>0.6615176233216131</v>
       </c>
       <c r="K35">
-        <v>0.69234628378132079</v>
+        <v>0.6885457926009543</v>
       </c>
       <c r="L35">
-        <v>0.70347113652831328</v>
+        <v>0.6896511585056831</v>
       </c>
       <c r="M35">
-        <v>0.69717462158805599</v>
+        <v>0.6959619634835166</v>
       </c>
       <c r="N35">
-        <v>0.68307551659357579</v>
+        <v>0.6918110679065088</v>
       </c>
       <c r="O35">
-        <v>0.6710724974340434</v>
+        <v>0.6784057694478374</v>
       </c>
       <c r="P35">
-        <v>0.63378701230227508</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.6681849577634135</v>
+      </c>
+      <c r="Q35">
+        <v>0.6309942382083269</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>0.53689545812799222</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>0.60643796398459027</v>
+        <v>0.5360668123277386</v>
       </c>
       <c r="D36">
-        <v>0.65161474324001278</v>
+        <v>0.6046971604288011</v>
       </c>
       <c r="E36">
-        <v>0.68444126177669906</v>
+        <v>0.6505167694015325</v>
       </c>
       <c r="F36">
-        <v>0.67759222500955685</v>
+        <v>0.6836392903644904</v>
       </c>
       <c r="G36">
-        <v>0.68750280480122239</v>
+        <v>0.6760621684450985</v>
       </c>
       <c r="H36">
-        <v>0.68119476749380081</v>
+        <v>0.6853324182118103</v>
       </c>
       <c r="I36">
-        <v>0.6627127615216506</v>
+        <v>0.6788568752271996</v>
       </c>
       <c r="J36">
-        <v>0.69138577950329971</v>
+        <v>0.6554137996740256</v>
       </c>
       <c r="K36">
-        <v>0.6915586468319459</v>
+        <v>0.687052053497954</v>
       </c>
       <c r="L36">
-        <v>0.69443924062252171</v>
+        <v>0.6893428916837168</v>
       </c>
       <c r="M36">
-        <v>0.6883498123640388</v>
+        <v>0.7003383221023</v>
       </c>
       <c r="N36">
-        <v>0.67124680072961951</v>
+        <v>0.6935314632735827</v>
       </c>
       <c r="O36">
-        <v>0.66499396612834194</v>
+        <v>0.6806975016579528</v>
       </c>
       <c r="P36">
-        <v>0.63043301826988196</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.6758141482635321</v>
+      </c>
+      <c r="Q36">
+        <v>0.632889094963604</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>0.53590968593451738</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>0.60437776810114185</v>
+        <v>0.5557380828880008</v>
       </c>
       <c r="D37">
-        <v>0.65187333165990469</v>
+        <v>0.6117055435622959</v>
       </c>
       <c r="E37">
-        <v>0.68521103588555077</v>
+        <v>0.6709523780364955</v>
       </c>
       <c r="F37">
-        <v>0.67607370404604261</v>
+        <v>0.6648871020790968</v>
       </c>
       <c r="G37">
-        <v>0.68652192700655568</v>
+        <v>0.6318789990763184</v>
       </c>
       <c r="H37">
-        <v>0.6821830256698117</v>
+        <v>0.5753894715567748</v>
       </c>
       <c r="I37">
-        <v>0.65866623618627629</v>
+        <v>0.5843156126172591</v>
       </c>
       <c r="J37">
-        <v>0.68875987913877346</v>
+        <v>0.5686853891927358</v>
       </c>
       <c r="K37">
-        <v>0.68881340472996877</v>
+        <v>0.5539159800414292</v>
       </c>
       <c r="L37">
-        <v>0.69420918277593924</v>
+        <v>0.5560619508497946</v>
       </c>
       <c r="M37">
-        <v>0.68626574623867442</v>
+        <v>0.5358556692448403</v>
       </c>
       <c r="N37">
-        <v>0.66904416451891335</v>
+        <v>0.535048007259613</v>
       </c>
       <c r="O37">
-        <v>0.65773930081617593</v>
+        <v>0.5162278040946552</v>
       </c>
       <c r="P37">
-        <v>0.62279080265227937</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.4986930588808404</v>
+      </c>
+      <c r="Q37">
+        <v>0.4892822736717152</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>0.5373286562186167</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>0.60658865244109395</v>
+        <v>0.5566899095550858</v>
       </c>
       <c r="D38">
-        <v>0.65184232280944976</v>
+        <v>0.6207205531004582</v>
       </c>
       <c r="E38">
-        <v>0.68511399889041635</v>
+        <v>0.6768521859669576</v>
       </c>
       <c r="F38">
-        <v>0.67483231125327259</v>
+        <v>0.6721692352544337</v>
       </c>
       <c r="G38">
-        <v>0.68556522660131369</v>
+        <v>0.6342008133467043</v>
       </c>
       <c r="H38">
-        <v>0.67946633796587663</v>
+        <v>0.582485606835901</v>
       </c>
       <c r="I38">
-        <v>0.66070936105043598</v>
+        <v>0.6160019285310984</v>
       </c>
       <c r="J38">
-        <v>0.68888450519631494</v>
+        <v>0.611696799977627</v>
       </c>
       <c r="K38">
-        <v>0.68990287198779909</v>
+        <v>0.6277542222179922</v>
       </c>
       <c r="L38">
-        <v>0.69511268837556184</v>
+        <v>0.6537951806629676</v>
       </c>
       <c r="M38">
-        <v>0.69131429391794674</v>
+        <v>0.6446324031748518</v>
       </c>
       <c r="N38">
-        <v>0.67638212336803027</v>
+        <v>0.6355936963389235</v>
       </c>
       <c r="O38">
-        <v>0.66779228720198558</v>
+        <v>0.6363905098333207</v>
       </c>
       <c r="P38">
-        <v>0.62160397156593017</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.6156485974359006</v>
+      </c>
+      <c r="Q38">
+        <v>0.5768602330067278</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>0.53791013612636096</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>0.60610467211816088</v>
+        <v>0.5585670555606576</v>
       </c>
       <c r="D39">
-        <v>0.65343225951851935</v>
+        <v>0.626953151922489</v>
       </c>
       <c r="E39">
-        <v>0.68652668240401404</v>
+        <v>0.6803777528677346</v>
       </c>
       <c r="F39">
-        <v>0.67726021612038745</v>
+        <v>0.6733364916091318</v>
       </c>
       <c r="G39">
-        <v>0.6888988401411702</v>
+        <v>0.6377787630467397</v>
       </c>
       <c r="H39">
-        <v>0.67994716667953747</v>
+        <v>0.592240802756508</v>
       </c>
       <c r="I39">
-        <v>0.65843858913999997</v>
+        <v>0.6264371911811484</v>
       </c>
       <c r="J39">
-        <v>0.68966049262317974</v>
+        <v>0.6187157768807408</v>
       </c>
       <c r="K39">
-        <v>0.69137924086432367</v>
+        <v>0.6286561522724737</v>
       </c>
       <c r="L39">
-        <v>0.69603823477206461</v>
+        <v>0.6413284066735186</v>
       </c>
       <c r="M39">
-        <v>0.6901555295573657</v>
+        <v>0.6307985524511894</v>
       </c>
       <c r="N39">
-        <v>0.67884221581999893</v>
+        <v>0.62499512177283</v>
       </c>
       <c r="O39">
-        <v>0.6650567662359359</v>
+        <v>0.6299344834018032</v>
       </c>
       <c r="P39">
-        <v>0.62383529598082343</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.6262083673449332</v>
+      </c>
+      <c r="Q39">
+        <v>0.5960012929985471</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>0.53793247554654589</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>0.60615132508926983</v>
+        <v>0.5165823448616236</v>
       </c>
       <c r="D40">
-        <v>0.65002795780373757</v>
+        <v>0.4970656037628339</v>
       </c>
       <c r="E40">
-        <v>0.68362771793247534</v>
+        <v>0.5557917663276774</v>
       </c>
       <c r="F40">
-        <v>0.67365531859542738</v>
+        <v>0.6076634690730317</v>
       </c>
       <c r="G40">
-        <v>0.6830479848619242</v>
+        <v>0.6141546117745208</v>
       </c>
       <c r="H40">
-        <v>0.67657431550782221</v>
+        <v>0.6142277442241016</v>
       </c>
       <c r="I40">
-        <v>0.65084853501762563</v>
+        <v>0.6006305108011559</v>
       </c>
       <c r="J40">
-        <v>0.68478122013357734</v>
+        <v>0.5934252005583123</v>
       </c>
       <c r="K40">
-        <v>0.68846893386077301</v>
+        <v>0.5847081503177848</v>
       </c>
       <c r="L40">
-        <v>0.70118579107292744</v>
+        <v>0.5542701393035562</v>
       </c>
       <c r="M40">
-        <v>0.6934407159213184</v>
+        <v>0.5190969342671661</v>
       </c>
       <c r="N40">
-        <v>0.68048523752501278</v>
+        <v>0.4884978583759547</v>
       </c>
       <c r="O40">
-        <v>0.67400157301244834</v>
+        <v>0.4561978878118432</v>
       </c>
       <c r="P40">
-        <v>0.63349883813130914</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.4272489741996677</v>
+      </c>
+      <c r="Q40">
+        <v>0.377549901654811</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.55550493726214845</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>0.61921413031763006</v>
+        <v>0.5091230184332226</v>
       </c>
       <c r="D41">
-        <v>0.6759544923668539</v>
+        <v>0.5507573657442475</v>
       </c>
       <c r="E41">
-        <v>0.66737241242795498</v>
+        <v>0.5333885071204092</v>
       </c>
       <c r="F41">
-        <v>0.63406121573267815</v>
+        <v>0.498470474032775</v>
       </c>
       <c r="G41">
-        <v>0.57698601339105526</v>
+        <v>0.4490613098588008</v>
       </c>
       <c r="H41">
-        <v>0.5863546254861618</v>
+        <v>0.423751271567113</v>
       </c>
       <c r="I41">
-        <v>0.56853694481168982</v>
+        <v>0.4305705568305406</v>
       </c>
       <c r="J41">
-        <v>0.55220103171711699</v>
+        <v>0.4423609475857529</v>
       </c>
       <c r="K41">
-        <v>0.55405339812545307</v>
+        <v>0.4328442310788912</v>
       </c>
       <c r="L41">
-        <v>0.53377919786722272</v>
+        <v>0.3563491590425572</v>
       </c>
       <c r="M41">
-        <v>0.53423320745651548</v>
+        <v>0.2982261909827487</v>
       </c>
       <c r="N41">
-        <v>0.51814383781822548</v>
+        <v>0.2702758340961906</v>
       </c>
       <c r="O41">
-        <v>0.49920394176560889</v>
+        <v>0.211031011485682</v>
       </c>
       <c r="P41">
-        <v>0.48786712940817539</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.1770695851844173</v>
+      </c>
+      <c r="Q41">
+        <v>0.1989437827238904</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>0.5571894147221913</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>0.62403933170222248</v>
+        <v>0.4121345679692312</v>
       </c>
       <c r="D42">
-        <v>0.67812511990570234</v>
+        <v>0.5246201617917819</v>
       </c>
       <c r="E42">
-        <v>0.67118547195871525</v>
+        <v>0.5179384529927576</v>
       </c>
       <c r="F42">
-        <v>0.63394529487125129</v>
+        <v>0.5243498996085701</v>
       </c>
       <c r="G42">
-        <v>0.58566694379866757</v>
+        <v>0.460243198113066</v>
       </c>
       <c r="H42">
-        <v>0.61647175172830893</v>
+        <v>0.4773120620469794</v>
       </c>
       <c r="I42">
-        <v>0.60848127286810838</v>
+        <v>0.4743189857728262</v>
       </c>
       <c r="J42">
-        <v>0.62600605925763586</v>
+        <v>0.4269662913179795</v>
       </c>
       <c r="K42">
-        <v>0.65252517901111573</v>
+        <v>0.3557424475066773</v>
       </c>
       <c r="L42">
-        <v>0.64170540338511894</v>
+        <v>0.292080679582077</v>
       </c>
       <c r="M42">
-        <v>0.63158390866027814</v>
+        <v>0.2747107836280084</v>
       </c>
       <c r="N42">
-        <v>0.63364463865013054</v>
+        <v>0.2645371255619399</v>
       </c>
       <c r="O42">
-        <v>0.61646655676683737</v>
+        <v>0.2398804579471119</v>
       </c>
       <c r="P42">
-        <v>0.57846870707577835</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.2243007578889999</v>
+      </c>
+      <c r="Q42">
+        <v>0.2251519756451524</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>0.5567449878947881</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>0.62114186751852707</v>
+        <v>0.5305625170992809</v>
       </c>
       <c r="D43">
-        <v>0.67652155098045963</v>
+        <v>0.5221791777109712</v>
       </c>
       <c r="E43">
-        <v>0.66844094378997165</v>
+        <v>0.5100859631551016</v>
       </c>
       <c r="F43">
-        <v>0.63497646951032993</v>
+        <v>0.4849554371158496</v>
       </c>
       <c r="G43">
-        <v>0.58385771889908589</v>
+        <v>0.4112884354384042</v>
       </c>
       <c r="H43">
-        <v>0.61532314291731049</v>
+        <v>0.435858712699535</v>
       </c>
       <c r="I43">
-        <v>0.60778134763525626</v>
+        <v>0.4602984719972651</v>
       </c>
       <c r="J43">
-        <v>0.61778526285745372</v>
+        <v>0.4757530532259671</v>
       </c>
       <c r="K43">
-        <v>0.63135651475005183</v>
+        <v>0.4119269134562105</v>
       </c>
       <c r="L43">
-        <v>0.62648864431690965</v>
+        <v>0.4156833308743682</v>
       </c>
       <c r="M43">
-        <v>0.61704274221703048</v>
+        <v>0.3789320292755036</v>
       </c>
       <c r="N43">
-        <v>0.62450306853277471</v>
+        <v>0.365828896855804</v>
       </c>
       <c r="O43">
-        <v>0.61955105756023721</v>
+        <v>0.3728596412062046</v>
       </c>
       <c r="P43">
-        <v>0.5919103540876165</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44">
-        <v>0.51818993768802069</v>
-      </c>
-      <c r="C44">
-        <v>0.50343149693115852</v>
-      </c>
-      <c r="D44">
-        <v>0.56053383399257284</v>
-      </c>
-      <c r="E44">
-        <v>0.61140600802542688</v>
-      </c>
-      <c r="F44">
-        <v>0.6174652657910531</v>
-      </c>
-      <c r="G44">
-        <v>0.62186775560155916</v>
-      </c>
-      <c r="H44">
-        <v>0.60285881459982504</v>
-      </c>
-      <c r="I44">
-        <v>0.59855277440842658</v>
-      </c>
-      <c r="J44">
-        <v>0.58884182026598175</v>
-      </c>
-      <c r="K44">
-        <v>0.55592724831584983</v>
-      </c>
-      <c r="L44">
-        <v>0.5195299951164748</v>
-      </c>
-      <c r="M44">
-        <v>0.48990532306480328</v>
-      </c>
-      <c r="N44">
-        <v>0.4616592370555393</v>
-      </c>
-      <c r="O44">
-        <v>0.43186043217522219</v>
-      </c>
-      <c r="P44">
-        <v>0.38132760445014302</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45">
-        <v>0.50818896628040922</v>
-      </c>
-      <c r="C45">
-        <v>0.54657360083707052</v>
-      </c>
-      <c r="D45">
-        <v>0.53034973573516475</v>
-      </c>
-      <c r="E45">
-        <v>0.49904642736018529</v>
-      </c>
-      <c r="F45">
-        <v>0.45551228853409109</v>
-      </c>
-      <c r="G45">
-        <v>0.43628773498789192</v>
-      </c>
-      <c r="H45">
-        <v>0.4437640302740552</v>
-      </c>
-      <c r="I45">
-        <v>0.44826256989585372</v>
-      </c>
-      <c r="J45">
-        <v>0.43702410430934252</v>
-      </c>
-      <c r="K45">
-        <v>0.36434384439770801</v>
-      </c>
-      <c r="L45">
-        <v>0.30303189485004062</v>
-      </c>
-      <c r="M45">
-        <v>0.27375110458232982</v>
-      </c>
-      <c r="N45">
-        <v>0.21720869396933079</v>
-      </c>
-      <c r="O45">
-        <v>0.19062667465035549</v>
-      </c>
-      <c r="P45">
-        <v>0.21107025411203459</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46">
-        <v>0.41564541635567231</v>
-      </c>
-      <c r="C46">
-        <v>0.52794463695948901</v>
-      </c>
-      <c r="D46">
-        <v>0.5262297862251607</v>
-      </c>
-      <c r="E46">
-        <v>0.52733212668426066</v>
-      </c>
-      <c r="F46">
-        <v>0.46905732986448739</v>
-      </c>
-      <c r="G46">
-        <v>0.48261748596722681</v>
-      </c>
-      <c r="H46">
-        <v>0.48340494641242082</v>
-      </c>
-      <c r="I46">
-        <v>0.43959557811508171</v>
-      </c>
-      <c r="J46">
-        <v>0.36739561054141362</v>
-      </c>
-      <c r="K46">
-        <v>0.29686349739613899</v>
-      </c>
-      <c r="L46">
-        <v>0.27531122259186042</v>
-      </c>
-      <c r="M46">
-        <v>0.26913943820960728</v>
-      </c>
-      <c r="N46">
-        <v>0.24383457465642011</v>
-      </c>
-      <c r="O46">
-        <v>0.22865838251651599</v>
-      </c>
-      <c r="P46">
-        <v>0.23312820607189499</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47">
-        <v>0.52806500155134972</v>
-      </c>
-      <c r="C47">
-        <v>0.5170487152013612</v>
-      </c>
-      <c r="D47">
-        <v>0.50361264985950815</v>
-      </c>
-      <c r="E47">
-        <v>0.47943856368576387</v>
-      </c>
-      <c r="F47">
-        <v>0.40432536799439928</v>
-      </c>
-      <c r="G47">
-        <v>0.43106732420256899</v>
-      </c>
-      <c r="H47">
-        <v>0.45479994926881601</v>
-      </c>
-      <c r="I47">
-        <v>0.47099834829240922</v>
-      </c>
-      <c r="J47">
-        <v>0.40712128474174308</v>
-      </c>
-      <c r="K47">
-        <v>0.40858693773966859</v>
-      </c>
-      <c r="L47">
-        <v>0.37279023256144622</v>
-      </c>
-      <c r="M47">
-        <v>0.3557505069269522</v>
-      </c>
-      <c r="N47">
-        <v>0.36368329642042252</v>
-      </c>
-      <c r="O47">
-        <v>0.36558029668146907</v>
-      </c>
-      <c r="P47">
-        <v>0.36504565916542348</v>
+        <v>0.3738513255430004</v>
+      </c>
+      <c r="Q43">
+        <v>0.3750132800228609</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P47">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>